--- a/database.xlsx
+++ b/database.xlsx
@@ -34,8 +34,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="d-mmm-yy"/>
+    <numFmt numFmtId="165" formatCode="d-mmmm-yy"/>
+    <numFmt numFmtId="166" formatCode="dd-mmmm-yy"/>
+    <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -399,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -447,25 +451,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Digital Procurement Portal Integration</v>
+        <v>BP</v>
       </c>
       <c r="C2" t="str">
-        <v>Develop and deploy a centralized web portal to digitize all vendor onboarding, bidding, and purchase order tracking.</v>
+        <v>Develop and integrate the Business Process forms, master data mapping, and agent orchestration workflows.</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-06-30</v>
+        <v>2026-05-22</v>
       </c>
       <c r="F2">
-        <v>4500000</v>
+        <v>3500000</v>
       </c>
       <c r="G2">
-        <v>3200000</v>
+        <v>2885750</v>
       </c>
       <c r="H2" t="str">
-        <v>Aarav Mehta</v>
+        <v>Ananth</v>
       </c>
       <c r="I2" t="str">
         <v>corporate procurement digital</v>
@@ -474,13 +478,13 @@
         <v>delayed</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-01-12</v>
+        <v>2026-02-11</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -488,40 +492,40 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Steel Foundry Capex Expansion</v>
+        <v>Leasing Automation</v>
       </c>
       <c r="C3" t="str">
-        <v>Install new electric arc furnace and expand foundry capacity at Odisha plant to meet increasing steel demand.</v>
+        <v>Automate and streamline the leasing process lifecycle up to Purchase Order creation.</v>
       </c>
       <c r="D3" t="str">
-        <v>2025-11-01</v>
+        <v>2026-04-15</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-05-31</v>
+        <v>2026-09-16</v>
       </c>
       <c r="F3">
-        <v>15000000</v>
+        <v>4500000</v>
       </c>
       <c r="G3">
-        <v>14200000</v>
+        <v>612000</v>
       </c>
       <c r="H3" t="str">
-        <v>Rajesh Singh</v>
+        <v>Mehrshad Nava</v>
       </c>
       <c r="I3" t="str">
-        <v>steel</v>
+        <v>finance</v>
       </c>
       <c r="J3" t="str">
-        <v>completed</v>
+        <v>delayed</v>
       </c>
       <c r="K3" t="str">
-        <v>2025-11-01</v>
+        <v>2026-04-15</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-06-10</v>
+        <v/>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -529,52 +533,380 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>EXIM Trade Banking API Automation</v>
+        <v>eBRC</v>
       </c>
       <c r="C4" t="str">
-        <v>Automate letter of credit and bank guarantee issuance processes with banking partner APIs for export operations.</v>
+        <v>Integrate electronic Bank Realization Certificate fetching and automated reconciliation services.</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-01</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-31</v>
+        <v>2026-04-29</v>
       </c>
       <c r="F4">
         <v>2500000</v>
       </c>
       <c r="G4">
-        <v>1100000</v>
+        <v>2103750</v>
       </c>
       <c r="H4" t="str">
-        <v>Divya Iyer</v>
+        <v>Ivan</v>
       </c>
       <c r="I4" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J4" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Forex</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Build a real-time Forex dashboard displaying replicas, MTM reports, and what-if analysis.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F5">
+        <v>3500000</v>
+      </c>
+      <c r="G5">
+        <v>2945250</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I5" t="str">
+        <v>finance</v>
+      </c>
+      <c r="J5" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K5" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>IDPMS Dashboard</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Create a consolidated Import Data Processing and Monitoring System dashboard for import tracking.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="F6">
+        <v>4500000</v>
+      </c>
+      <c r="G6">
+        <v>3825000</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I6" t="str">
         <v>banking</v>
       </c>
-      <c r="J4" t="str">
+      <c r="J6" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K6" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Bill of Entry</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Automate custom details extraction using scripts and process mapping for custom clearance.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F7">
+        <v>2500000</v>
+      </c>
+      <c r="G7">
+        <v>680000</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I7" t="str">
+        <v>imports</v>
+      </c>
+      <c r="J7" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K7" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Bill of Entry Checklist</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Develop, implement, and run checklist validation scripts for Bill of Entry files.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="F8">
+        <v>3500000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I8" t="str">
+        <v>imports</v>
+      </c>
+      <c r="J8" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Pre-Import Condition Controls in LN</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Configure and deploy pre-import compliance condition controls inside Infor LN ERP.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F9">
+        <v>4500000</v>
+      </c>
+      <c r="G9">
+        <v>1262250</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I9" t="str">
+        <v>imports</v>
+      </c>
+      <c r="J9" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-03-03</v>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="M9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Banking API Integration</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Secure API integration with banking partners including token engines and callback webhooks.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F10">
+        <v>2500000</v>
+      </c>
+      <c r="G10">
+        <v>2018750</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Ivan &amp; Ananth</v>
+      </c>
+      <c r="I10" t="str">
+        <v>banking</v>
+      </c>
+      <c r="J10" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ITR-1 Dashboard</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Implement portfolio dashboards for automated income tax return tracking (ITR-1).</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F11">
+        <v>3500000</v>
+      </c>
+      <c r="G11">
+        <v>2826250</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I11" t="str">
+        <v>it</v>
+      </c>
+      <c r="J11" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Steel Dashboard Enhancements</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Upgrade the Steel department dashboard to assist with stockout decisions, hedge decisions, and rate comparisons.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F12">
+        <v>4500000</v>
+      </c>
+      <c r="G12">
+        <v>726750</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I12" t="str">
+        <v>steel</v>
+      </c>
+      <c r="J12" t="str">
         <v>on-track</v>
       </c>
-      <c r="K4" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4">
-        <v>45</v>
+      <c r="K12" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N109"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -628,25 +960,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>Requirement Specification</v>
+        <v>Requirement gathering</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-10</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-27</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-01-12</v>
+        <v>2026-02-11</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-27</v>
       </c>
       <c r="H2" t="str">
-        <v>Aarav Mehta</v>
+        <v>Ananth &amp; Ivan</v>
       </c>
       <c r="I2" t="str">
-        <v>completed</v>
+        <v>in-progress</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -661,7 +993,7 @@
         <v/>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -672,22 +1004,22 @@
         <v>1.1</v>
       </c>
       <c r="C3" t="str">
-        <v>Vendor Registration Workflow</v>
+        <v>Business requirement</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-15</v>
+        <v>2026-02-11</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-02-05</v>
+        <v>2026-02-13</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-01-15</v>
+        <v>2026-02-11</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-02-04</v>
+        <v>2026-02-13</v>
       </c>
       <c r="H3" t="str">
-        <v>Neha Sharma</v>
+        <v>Ananth &amp; Ivan</v>
       </c>
       <c r="I3" t="str">
         <v>completed</v>
@@ -713,25 +1045,25 @@
         <v>1</v>
       </c>
       <c r="B4" t="str">
-        <v>1.2</v>
+        <v>1.1.1</v>
       </c>
       <c r="C4" t="str">
-        <v>PO Approval Flow Definition</v>
+        <v>Process mapping (As‑Is / To‑Be)</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-01</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-18</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-02-02</v>
+        <v>2026-02-16</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-18</v>
       </c>
       <c r="H4" t="str">
-        <v>Rahul Verma</v>
+        <v>Ananth</v>
       </c>
       <c r="I4" t="str">
         <v>completed</v>
@@ -757,28 +1089,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="str">
-        <v>2</v>
+        <v>1.1.2</v>
       </c>
       <c r="C5" t="str">
-        <v>Portal Core Development</v>
+        <v>User journeys (Purchaser, Vendor, MDM)</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-05-15</v>
+        <v>2026-02-23</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-18</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2026-02-23</v>
       </c>
       <c r="H5" t="str">
-        <v>Amit Patel</v>
+        <v>Ananth</v>
       </c>
       <c r="I5" t="str">
-        <v>in-progress</v>
+        <v>completed</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -793,7 +1125,7 @@
         <v/>
       </c>
       <c r="N5">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -801,40 +1133,40 @@
         <v>1</v>
       </c>
       <c r="B6" t="str">
-        <v>2.1</v>
+        <v>1.1.3</v>
       </c>
       <c r="C6" t="str">
-        <v>MDM Database Synchronization</v>
+        <v>Agent identification &amp; scope</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-03-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-23</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-03-30</v>
+        <v>2026-02-27</v>
       </c>
       <c r="H6" t="str">
-        <v>Amit Patel</v>
+        <v>Ivan</v>
       </c>
       <c r="I6" t="str">
         <v>completed</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="str">
-        <v>Master Data Schema mismatched with legacy systems</v>
+        <v/>
       </c>
       <c r="L6" t="str">
-        <v>Database sync took 5 days extra</v>
+        <v/>
       </c>
       <c r="M6" t="str">
-        <v>Amit Patel</v>
+        <v/>
       </c>
       <c r="N6">
         <v>100</v>
@@ -845,28 +1177,28 @@
         <v>1</v>
       </c>
       <c r="B7" t="str">
-        <v>2.2</v>
+        <v>1.1.4</v>
       </c>
       <c r="C7" t="str">
-        <v>Bidding Module Implementation</v>
+        <v>Validation &amp; business‑rule definition</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-03-26</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-05-15</v>
+        <v>2026-02-27</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-04-01</v>
+        <v>2026-02-23</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2026-02-27</v>
       </c>
       <c r="H7" t="str">
-        <v>Neha Sharma</v>
+        <v>Ananth</v>
       </c>
       <c r="I7" t="str">
-        <v>in-progress</v>
+        <v>completed</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -881,7 +1213,7 @@
         <v/>
       </c>
       <c r="N7">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -889,43 +1221,43 @@
         <v>1</v>
       </c>
       <c r="B8" t="str">
-        <v>2.2.1</v>
+        <v>1.2</v>
       </c>
       <c r="C8" t="str">
-        <v>Reverse Auction Engine</v>
+        <v>Cost Approval from RDC</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-03-26</v>
+        <v>2026-05-18</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-04-20</v>
+        <v>2026-05-22</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-04-01</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>2026-04-25</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>Neha Sharma</v>
+        <v>RDC</v>
       </c>
       <c r="I8" t="str">
-        <v>completed</v>
+        <v>delayed</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="K8" t="str">
-        <v>Complex business logic approval from finance was delayed</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
       </c>
       <c r="L8" t="str">
-        <v>Reverse auction deployment delayed by 5 days</v>
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="M8" t="str">
-        <v>Aarav Mehta</v>
+        <v>RDC</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1265,25 @@
         <v>1</v>
       </c>
       <c r="B9" t="str">
-        <v>2.2.2</v>
+        <v>2</v>
       </c>
       <c r="C9" t="str">
-        <v>Bid Security Verification</v>
+        <v>Development</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-21</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-22</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-04-26</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Rahul Verma</v>
+        <v>Us &amp; GITL</v>
       </c>
       <c r="I9" t="str">
         <v>in-progress</v>
@@ -969,36 +1301,36 @@
         <v/>
       </c>
       <c r="N9">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="str">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="C10" t="str">
-        <v>Site Preparation &amp; Foundation Work</v>
+        <v>Frontend</v>
       </c>
       <c r="D10" t="str">
-        <v>2025-11-01</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E10" t="str">
-        <v>2025-12-15</v>
+        <v>2026-05-15</v>
       </c>
       <c r="F10" t="str">
-        <v>2025-11-01</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G10" t="str">
-        <v>2025-12-15</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Rajesh Singh</v>
+        <v>Us &amp; GITL</v>
       </c>
       <c r="I10" t="str">
-        <v>completed</v>
+        <v>in-progress</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1013,77 +1345,77 @@
         <v/>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="str">
-        <v>2</v>
+        <v>2.1.1</v>
       </c>
       <c r="C11" t="str">
-        <v>Furnace Procurement &amp; Import</v>
+        <v>Purchaser Form</v>
       </c>
       <c r="D11" t="str">
-        <v>2025-12-16</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-03-10</v>
+        <v>2026-05-08</v>
       </c>
       <c r="F11" t="str">
-        <v>2025-12-20</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-03-25</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Vikram Malhotra</v>
+        <v>Us &amp; GITL</v>
       </c>
       <c r="I11" t="str">
-        <v>completed</v>
+        <v>in-progress</v>
       </c>
       <c r="J11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K11" t="str">
-        <v>Suez Canal route congestion delayed customs clearance at Mumbai port</v>
+        <v/>
       </c>
       <c r="L11" t="str">
-        <v>Furnace arrival delayed by 15 days</v>
+        <v/>
       </c>
       <c r="M11" t="str">
-        <v>Vikram Malhotra</v>
+        <v/>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="str">
-        <v>2.1</v>
+        <v>2.1.1.1</v>
       </c>
       <c r="C12" t="str">
-        <v>Customs Clearance &amp; EXIM Paperwork</v>
+        <v>Mapping of fields</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-10</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-03-10</v>
+        <v>2026-02-27</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-03-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="H12" t="str">
-        <v>Vikram Malhotra</v>
+        <v>Ananth</v>
       </c>
       <c r="I12" t="str">
         <v>completed</v>
@@ -1106,28 +1438,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="str">
-        <v>3</v>
+        <v>2.1.1.2</v>
       </c>
       <c r="C13" t="str">
-        <v>Erection &amp; Commissioning</v>
+        <v>Field wise controls and measures</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-03-11</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-05-31</v>
+        <v>2026-03-02</v>
       </c>
       <c r="F13" t="str">
-        <v>2026-03-26</v>
+        <v>2026-02-27</v>
       </c>
       <c r="G13" t="str">
-        <v>2026-06-10</v>
+        <v>2026-03-02</v>
       </c>
       <c r="H13" t="str">
-        <v>Sanjay Dutt</v>
+        <v>Ananth</v>
       </c>
       <c r="I13" t="str">
         <v>completed</v>
@@ -1150,75 +1482,75 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" t="str">
-        <v>1</v>
+        <v>2.1.1.3</v>
       </c>
       <c r="C14" t="str">
-        <v>Banking API Integration Guide</v>
+        <v>Coding</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-03-01</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-04-10</v>
+        <v>2026-05-08</v>
       </c>
       <c r="F14" t="str">
-        <v>2026-03-05</v>
+        <v>2026-04-20</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-04-12</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v>Kunal Sen</v>
+        <v>GITL</v>
       </c>
       <c r="I14" t="str">
-        <v>completed</v>
+        <v>delayed</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>Operational bottlenecks and resource allocation delays.</v>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>GITL</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" t="str">
-        <v>2</v>
+        <v>2.1.2</v>
       </c>
       <c r="C15" t="str">
-        <v>API Security &amp; Token Engine</v>
+        <v>Vendor Form</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-11</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-05-31</v>
+        <v>2026-05-08</v>
       </c>
       <c r="F15" t="str">
-        <v>2026-04-13</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-05-30</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Kunal Sen</v>
+        <v>Us &amp; GITL</v>
       </c>
       <c r="I15" t="str">
-        <v>completed</v>
+        <v>in-progress</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1233,36 +1565,36 @@
         <v/>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B16" t="str">
-        <v>3</v>
+        <v>2.1.2.1</v>
       </c>
       <c r="C16" t="str">
-        <v>Letter of Credit Automation Module</v>
+        <v>Mapping of fields</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-06-01</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-31</v>
+        <v>2026-02-27</v>
       </c>
       <c r="F16" t="str">
-        <v>2026-06-01</v>
+        <v>2026-02-25</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>2026-02-27</v>
       </c>
       <c r="H16" t="str">
-        <v>Divya Iyer</v>
+        <v>Ananth</v>
       </c>
       <c r="I16" t="str">
-        <v>in-progress</v>
+        <v>completed</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1277,36 +1609,36 @@
         <v/>
       </c>
       <c r="N16">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="str">
-        <v>3.1</v>
+        <v>2.1.2.2</v>
       </c>
       <c r="C17" t="str">
-        <v>Draft LC Generation Form</v>
+        <v>Field wise controls and measures</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-06-01</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-15</v>
+        <v>2026-03-02</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-06-02</v>
+        <v>2026-02-27</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>2026-03-02</v>
       </c>
       <c r="H17" t="str">
-        <v>Meera Nair</v>
+        <v>Ananth</v>
       </c>
       <c r="I17" t="str">
-        <v>in-progress</v>
+        <v>completed</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1321,63 +1653,4067 @@
         <v/>
       </c>
       <c r="N17">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2.1.2.3</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Coding</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I18" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J18">
+        <v>36</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M18" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2.1.3</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I19" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>1</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2.1.3.1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Unit tests</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I20" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J20">
+        <v>31</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M20" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2.1.3.2</v>
+      </c>
+      <c r="C21" t="str">
+        <v>UI validation tests</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I21" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J21">
+        <v>29</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M21" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Backend</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I22" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2.2.1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Backend development</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I23" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J23">
+        <v>36</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M23" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N23">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2.2.2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>API Integration</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I24" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>1</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2.2.2.1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>API wise integration</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I25" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J25">
+        <v>36</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M25" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2.2.2.2</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Error &amp; timeout handling</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I26" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J26">
+        <v>36</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M26" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N26">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>1</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2.2.2.3</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Retry &amp; fallback logic</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I27" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J27">
+        <v>36</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M27" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N27">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>1</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2.2.3</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Database Schema</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F28" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I28" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J28">
+        <v>36</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M28" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N28">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>1</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2.2.4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Integration with Frontend</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F29" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I29" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J29">
+        <v>36</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M29" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N29">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>1</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2.2.5</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I30" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>1</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2.2.5.1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Unit tests</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I31" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J31">
+        <v>29</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M31" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>1</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2.2.5.2</v>
+      </c>
+      <c r="C32" t="str">
+        <v>API contract tests</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I32" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J32">
+        <v>29</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M32" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>1</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Agents</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I33" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>1</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2.3.1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Mapping of agents</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I34" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>1</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2.3.2</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Coding of agents</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E35" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I35" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J35">
+        <v>36</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="N35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>1</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2.3.3</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Coding of individual agents</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F36" t="str">
+        <v>2026-03-17</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I36" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J36">
+        <v>36</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="N36">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>1</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2.3.4</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Combine similar agents wherever possible</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E37" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F37" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I37" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J37">
+        <v>36</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="N37">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2.3.5</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Agent Orchestration</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I38" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J38">
+        <v>29</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>1</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2.3.6</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Agent Testing</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E39" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I39" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J39">
+        <v>22</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>1</v>
+      </c>
+      <c r="B40" t="str">
         <v>3</v>
       </c>
-      <c r="B18" t="str">
+      <c r="C40" t="str">
+        <v>Documentation</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E40" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="F40" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I40" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J40">
+        <v>22</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="N40">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2</v>
+      </c>
+      <c r="B41" t="str">
+        <v>1</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Process Mapping</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F41" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="I41" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2</v>
+      </c>
+      <c r="B42" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Steps till PO Creation</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E42" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F42" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I42" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J42">
+        <v>19</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Metting set with Mikhil sir 30-06</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="N42">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2</v>
+      </c>
+      <c r="B43" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Discussion / issue resolving</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>GITL / internal</v>
+      </c>
+      <c r="I43" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J43">
+        <v>19</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M43" t="str">
+        <v>GITL / internal</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Finalizing Flow</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F44" t="str">
+        <v>2026-04-25</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I44" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J44">
+        <v>19</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="N44">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2</v>
+      </c>
+      <c r="B45" t="str">
+        <v>1.4</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Document flow After PO Ctreation</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F45" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="I45" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2</v>
+      </c>
+      <c r="B46" t="str">
+        <v>1.4.1</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Mapping as it Process for Mizuho</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F46" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="G46" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="I46" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2</v>
+      </c>
+      <c r="B47" t="str">
+        <v>1.4.2</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Mapping as it Process ORIX / HPFS</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F47" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="G47" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="I47" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2</v>
+      </c>
+      <c r="B48" t="str">
+        <v>1.4.3</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Finalizing Flow</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="F48" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I48" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Agent Identification &amp; scope</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I49" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C50" t="str">
+        <v>First cut of Agentic break</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I50" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J50">
+        <v>26</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Finalization of Agentic break</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="I51" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J51">
+        <v>24</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2</v>
+      </c>
+      <c r="B52" t="str">
+        <v>3</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Discussion with DIGITAL / GITL</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="I52" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J52">
+        <v>14</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2</v>
+      </c>
+      <c r="B53" t="str">
+        <v>4</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Development</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="I53" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2</v>
+      </c>
+      <c r="B54" t="str">
+        <v>4.1</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Speedflow data access</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I54" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2</v>
+      </c>
+      <c r="B55" t="str">
+        <v>4.2</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Frontend</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I55" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2</v>
+      </c>
+      <c r="B56" t="str">
+        <v>4.3</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Backend</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="I56" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2</v>
+      </c>
+      <c r="B57" t="str">
+        <v>4.4</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Agent development</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="I57" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2</v>
+      </c>
+      <c r="B58" t="str">
+        <v>5</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Tesing</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="I58" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2</v>
+      </c>
+      <c r="B59" t="str">
+        <v>6</v>
+      </c>
+      <c r="C59" t="str">
+        <v>live</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="I59" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>3</v>
+      </c>
+      <c r="B60" t="str">
+        <v>1</v>
+      </c>
+      <c r="C60" t="str">
+        <v>IEC Branch Mapping</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="F60" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="G60" t="str">
+        <v>2026-02-27</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Ivan Charit</v>
+      </c>
+      <c r="I60" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>3</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Moving current fetching of IRM data to Production</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="F61" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="G61" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I61" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>3</v>
+      </c>
+      <c r="B62" t="str">
+        <v>3</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Meeting to decide on the final system</v>
+      </c>
+      <c r="D62" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="F62" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="G62" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="I62" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>3</v>
+      </c>
+      <c r="B63" t="str">
+        <v>4</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Prototype and testing</v>
+      </c>
+      <c r="D63" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="F63" t="str">
+        <v>2026-03-23</v>
+      </c>
+      <c r="G63" t="str">
+        <v>2026-04-08</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="I63" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>3</v>
+      </c>
+      <c r="B64" t="str">
+        <v>5</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Writing Code</v>
+      </c>
+      <c r="D64" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E64" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="F64" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="G64" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="I64" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>3</v>
+      </c>
+      <c r="B65" t="str">
+        <v>6</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D65" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2026-04-22</v>
+      </c>
+      <c r="F65" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="G65" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="I65" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J65">
+        <v>23</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="N65">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>3</v>
+      </c>
+      <c r="B66" t="str">
+        <v>7</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Go live</v>
+      </c>
+      <c r="D66" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="F66" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I66" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J66">
+        <v>45</v>
+      </c>
+      <c r="K66" t="str">
+        <v>planned end date 5th june</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M66" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N66">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>4</v>
+      </c>
+      <c r="B67" t="str">
+        <v>1</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Finalizing dashboard layout for current replica</v>
+      </c>
+      <c r="D67" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="F67" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="G67" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I67" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>4</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2</v>
+      </c>
+      <c r="C68" t="str">
+        <v>(OTRS) Provision to upload existing contract and other details</v>
+      </c>
+      <c r="D68" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="F68" t="str">
+        <v>2026-02-11</v>
+      </c>
+      <c r="G68" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I68" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>4</v>
+      </c>
+      <c r="B69" t="str">
+        <v>3</v>
+      </c>
+      <c r="C69" t="str">
+        <v>(SRF) Provision to upload existing contract and other details</v>
+      </c>
+      <c r="D69" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="F69" t="str">
+        <v>2026-02-13</v>
+      </c>
+      <c r="G69" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I69" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>4</v>
+      </c>
+      <c r="B70" t="str">
+        <v>4</v>
+      </c>
+      <c r="C70" t="str">
+        <v>(New SRF) Provision to upload existing contract and other details</v>
+      </c>
+      <c r="D70" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="F70" t="str">
+        <v>2026-04-06</v>
+      </c>
+      <c r="G70" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I70" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>4</v>
+      </c>
+      <c r="B71" t="str">
+        <v>5</v>
+      </c>
+      <c r="C71" t="str">
+        <v>(FSD) Provision to upload existing contract and other details</v>
+      </c>
+      <c r="D71" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="F71" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="G71" t="str">
+        <v>2026-05-06</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I71" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="N71">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>4</v>
+      </c>
+      <c r="B72" t="str">
+        <v>6</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Development</v>
+      </c>
+      <c r="D72" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F72" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I72" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M72" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="N72">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>4</v>
+      </c>
+      <c r="B73" t="str">
+        <v>7</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Building the dashboard as per requirements</v>
+      </c>
+      <c r="D73" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="F73" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="G73" t="str">
+        <v>2026-03-13</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I73" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>4</v>
+      </c>
+      <c r="B74" t="str">
+        <v>8</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Added new Dashboard page for MTM</v>
+      </c>
+      <c r="D74" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F74" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I74" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>4</v>
+      </c>
+      <c r="B75" t="str">
+        <v>8.1</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Normal MTM report as per bank</v>
+      </c>
+      <c r="D75" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="F75" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="G75" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I75" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>4</v>
+      </c>
+      <c r="B76" t="str">
+        <v>8.2</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Gain/Loss Report</v>
+      </c>
+      <c r="D76" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F76" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="G76" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I76" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>4</v>
+      </c>
+      <c r="B77" t="str">
+        <v>8.3</v>
+      </c>
+      <c r="C77" t="str">
+        <v>What-If Analysis</v>
+      </c>
+      <c r="D77" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I77" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J77">
+        <v>29</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>5</v>
+      </c>
+      <c r="B78" t="str">
+        <v>1</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Data Mapping</v>
+      </c>
+      <c r="D78" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="F78" t="str">
+        <v>2026-05-04</v>
+      </c>
+      <c r="G78" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Charit &amp; Vaishanvi</v>
+      </c>
+      <c r="I78" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>5</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Dashboard 1st Cut</v>
+      </c>
+      <c r="D79" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F79" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="G79" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I79" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>5</v>
+      </c>
+      <c r="B80" t="str">
+        <v>3</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Changes and Modifications</v>
+      </c>
+      <c r="D80" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F80" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G80" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I80" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N80">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>5</v>
+      </c>
+      <c r="B81" t="str">
+        <v>4</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Final Testing</v>
+      </c>
+      <c r="D81" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F81" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="G81" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Charit &amp; Vaishanvi</v>
+      </c>
+      <c r="I81" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J81">
+        <v>5</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Charit &amp; Vaishanvi</v>
+      </c>
+      <c r="N81">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>5</v>
+      </c>
+      <c r="B82" t="str">
+        <v>5</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Dashboard Live</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="F82" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="G82" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I82" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J82">
+        <v>3</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>6</v>
+      </c>
+      <c r="B83" t="str">
+        <v>1</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Process Mapping</v>
+      </c>
+      <c r="D83" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="F83" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I83" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J83">
+        <v>34</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N83">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>6</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Detail extraction using Python Script</v>
+      </c>
+      <c r="D84" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="F84" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I84" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>6</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Fields mapping</v>
+      </c>
+      <c r="D85" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="E85" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="F85" t="str">
+        <v>2026-04-29</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I85" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J85">
+        <v>34</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N85">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>6</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Coding</v>
+      </c>
+      <c r="D86" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I86" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J86">
+        <v>14</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>6</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D87" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I87" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J87">
+        <v>14</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>6</v>
+      </c>
+      <c r="B88" t="str">
+        <v>3</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D88" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E88" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I88" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J88">
+        <v>14</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>6</v>
+      </c>
+      <c r="B89" t="str">
+        <v>4</v>
+      </c>
+      <c r="C89" t="str">
+        <v>creating flow to run the script</v>
+      </c>
+      <c r="D89" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I89" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J89">
+        <v>14</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>6</v>
+      </c>
+      <c r="B90" t="str">
+        <v>5</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Testing</v>
+      </c>
+      <c r="D90" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I90" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J90">
+        <v>8</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>6</v>
+      </c>
+      <c r="B91" t="str">
+        <v>6</v>
+      </c>
+      <c r="C91" t="str">
+        <v>live</v>
+      </c>
+      <c r="D91" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I91" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J91">
+        <v>7</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>7</v>
+      </c>
+      <c r="B92" t="str">
+        <v>1</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Script Developement</v>
+      </c>
+      <c r="D92" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I92" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>7</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Script testing</v>
+      </c>
+      <c r="D93" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-06-20</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I93" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>8</v>
+      </c>
+      <c r="B94" t="str">
+        <v>1</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Problem Discussion and Brainstorming</v>
+      </c>
+      <c r="D94" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="F94" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="G94" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Benefits, Division, Purchase Team</v>
+      </c>
+      <c r="I94" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>8</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2</v>
+      </c>
+      <c r="C95" t="str">
+        <v>SRF</v>
+      </c>
+      <c r="D95" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F95" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I95" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>8</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C96" t="str">
+        <v>SRF Preparation</v>
+      </c>
+      <c r="D96" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I96" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J96">
+        <v>8</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>8</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C97" t="str">
+        <v>SRF Raised &amp; Approved</v>
+      </c>
+      <c r="D97" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I97" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J97">
+        <v>4</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>8</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="C98" t="str">
+        <v>SRF CCB Approval &amp; Attach in system</v>
+      </c>
+      <c r="D98" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I98" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>8</v>
+      </c>
+      <c r="B99" t="str">
+        <v>3</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FSD</v>
+      </c>
+      <c r="D99" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I99" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>8</v>
+      </c>
+      <c r="B100" t="str">
+        <v>3.1</v>
+      </c>
+      <c r="C100" t="str">
+        <v>FSD Preparation</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-06-17</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I100" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>8</v>
+      </c>
+      <c r="B101" t="str">
         <v>3.2</v>
       </c>
-      <c r="C18" t="str">
-        <v>Bank API Callback Webhook</v>
-      </c>
-      <c r="D18" t="str">
-        <v>2026-07-16</v>
-      </c>
-      <c r="E18" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v>Meera Nair</v>
-      </c>
-      <c r="I18" t="str">
+      <c r="C101" t="str">
+        <v>FSD Approval</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I101" t="str">
         <v>not-started</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18">
-        <v>0</v>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>8</v>
+      </c>
+      <c r="B102" t="str">
+        <v>4</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Infor Developmet</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-06-26</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I102" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>8</v>
+      </c>
+      <c r="B103" t="str">
+        <v>5</v>
+      </c>
+      <c r="C103" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-06-29</v>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v>ALL</v>
+      </c>
+      <c r="I103" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>8</v>
+      </c>
+      <c r="B104" t="str">
+        <v>6</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Live</v>
+      </c>
+      <c r="D104" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="E104" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I104" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>9</v>
+      </c>
+      <c r="B105" t="str">
+        <v>1</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Problem Discussion and Brainstorming</v>
+      </c>
+      <c r="D105" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E105" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="F105" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v>Ivan &amp; Ananth</v>
+      </c>
+      <c r="I105" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J105">
+        <v>3</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L105" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M105" t="str">
+        <v>Ivan &amp; Ananth</v>
+      </c>
+      <c r="N105">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>10</v>
+      </c>
+      <c r="B106" t="str">
+        <v>1</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Modifications</v>
+      </c>
+      <c r="D106" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F106" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I106" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L106" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M106" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="N106">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>11</v>
+      </c>
+      <c r="B107" t="str">
+        <v>1</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Stockout Decision</v>
+      </c>
+      <c r="D107" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E107" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F107" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I107" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>11</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Rate Comparison</v>
+      </c>
+      <c r="D108" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F108" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="I108" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>11</v>
+      </c>
+      <c r="B109" t="str">
+        <v>3</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Hedge Decision</v>
+      </c>
+      <c r="D109" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="E109" t="str">
+        <v>2026-06-30</v>
+      </c>
+      <c r="F109" t="str">
+        <v>2026-06-09</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="I109" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N109"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1398,10 +5734,10 @@
         <v>tm1</v>
       </c>
       <c r="B2" t="str">
-        <v>Aarav Mehta</v>
+        <v>Ananth</v>
       </c>
       <c r="C2" t="str">
-        <v>Senior Project Manager</v>
+        <v>Senior Solutions Architect</v>
       </c>
       <c r="D2" t="str">
         <v>corporate procurement digital</v>
@@ -1412,13 +5748,13 @@
         <v>tm2</v>
       </c>
       <c r="B3" t="str">
-        <v>Rajesh Singh</v>
+        <v>Mehrshad Nava</v>
       </c>
       <c r="C3" t="str">
-        <v>Senior Project Manager</v>
+        <v>Lead Business Analyst</v>
       </c>
       <c r="D3" t="str">
-        <v>steel</v>
+        <v>finance</v>
       </c>
     </row>
     <row r="4">
@@ -1426,13 +5762,13 @@
         <v>tm3</v>
       </c>
       <c r="B4" t="str">
-        <v>Divya Iyer</v>
+        <v>Ivan</v>
       </c>
       <c r="C4" t="str">
-        <v>Senior Project Manager</v>
+        <v>Senior Workflow Engineer</v>
       </c>
       <c r="D4" t="str">
-        <v>banking</v>
+        <v>exports</v>
       </c>
     </row>
     <row r="5">
@@ -1440,13 +5776,13 @@
         <v>tm4</v>
       </c>
       <c r="B5" t="str">
-        <v>Neha Sharma</v>
+        <v>Charit</v>
       </c>
       <c r="C5" t="str">
-        <v>Lead Frontend Engineer</v>
+        <v>Lead Technical Architect</v>
       </c>
       <c r="D5" t="str">
-        <v>corporate procurement digital</v>
+        <v>banking</v>
       </c>
     </row>
     <row r="6">
@@ -1454,13 +5790,13 @@
         <v>tm5</v>
       </c>
       <c r="B6" t="str">
-        <v>Rahul Verma</v>
+        <v>Mehrshad</v>
       </c>
       <c r="C6" t="str">
-        <v>Workflow Designer</v>
+        <v>Lead Business Analyst</v>
       </c>
       <c r="D6" t="str">
-        <v>corporate procurement digital</v>
+        <v>imports</v>
       </c>
     </row>
     <row r="7">
@@ -1468,13 +5804,13 @@
         <v>tm6</v>
       </c>
       <c r="B7" t="str">
-        <v>Amit Patel</v>
+        <v>Ivan &amp; Ananth</v>
       </c>
       <c r="C7" t="str">
-        <v>Full Stack Developer</v>
+        <v>Core Technical Leads</v>
       </c>
       <c r="D7" t="str">
-        <v>corporate procurement digital</v>
+        <v>banking</v>
       </c>
     </row>
     <row r="8">
@@ -1482,13 +5818,13 @@
         <v>tm7</v>
       </c>
       <c r="B8" t="str">
-        <v>Vikram Malhotra</v>
+        <v>Ananth &amp; Ivan</v>
       </c>
       <c r="C8" t="str">
-        <v>EXIM Logistics Manager</v>
+        <v>Core Technical Lead Team</v>
       </c>
       <c r="D8" t="str">
-        <v>exports</v>
+        <v>corporate procurement digital</v>
       </c>
     </row>
     <row r="9">
@@ -1496,13 +5832,13 @@
         <v>tm8</v>
       </c>
       <c r="B9" t="str">
-        <v>Sanjay Dutt</v>
+        <v>RDC</v>
       </c>
       <c r="C9" t="str">
-        <v>Commissioning Engineer</v>
+        <v>Risk &amp; Compliance Sponsor</v>
       </c>
       <c r="D9" t="str">
-        <v>steel</v>
+        <v>corporate procurement digital</v>
       </c>
     </row>
     <row r="10">
@@ -1510,13 +5846,13 @@
         <v>tm9</v>
       </c>
       <c r="B10" t="str">
-        <v>Kunal Sen</v>
+        <v>Us &amp; GITL</v>
       </c>
       <c r="C10" t="str">
-        <v>API Security Engineer</v>
+        <v>Joint Implementation Partners</v>
       </c>
       <c r="D10" t="str">
-        <v>it</v>
+        <v>corporate procurement digital</v>
       </c>
     </row>
     <row r="11">
@@ -1524,18 +5860,144 @@
         <v>tm10</v>
       </c>
       <c r="B11" t="str">
-        <v>Meera Nair</v>
+        <v>GITL</v>
       </c>
       <c r="C11" t="str">
-        <v>Software Engineer</v>
+        <v>Offshore Team Lead</v>
       </c>
       <c r="D11" t="str">
+        <v>corporate procurement digital</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>tm11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Digital</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Digital Transformation Manager</v>
+      </c>
+      <c r="D12" t="str">
+        <v>corporate procurement digital</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>tm12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Charit Mehrshad</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Lead Technical Architect</v>
+      </c>
+      <c r="D13" t="str">
+        <v>finance</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>tm13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>GITL / internal</v>
+      </c>
+      <c r="C14" t="str">
+        <v>GITL Integration Leads</v>
+      </c>
+      <c r="D14" t="str">
+        <v>finance</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>tm14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Digital GITL</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Digital &amp; IT Steering Team</v>
+      </c>
+      <c r="D15" t="str">
+        <v>finance</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>tm15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Ivan Charit</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Technical Lead Pair</v>
+      </c>
+      <c r="D16" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>tm16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Ivan ananath</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Core Technical Leads</v>
+      </c>
+      <c r="D17" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>tm17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Charit &amp; Vaishanvi</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Feature Delivery Squad</v>
+      </c>
+      <c r="D18" t="str">
         <v>banking</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>tm18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Benefits, Division, Purchase Team</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Procurement Advisory Panel</v>
+      </c>
+      <c r="D19" t="str">
+        <v>imports</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>tm19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ALL</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Full Project Group</v>
+      </c>
+      <c r="D20" t="str">
+        <v>imports</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -445,6 +445,9 @@
       <c r="M1" t="str">
         <v>Project Progress</v>
       </c>
+      <c r="N1" t="str">
+        <v>Project Benefits</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -486,6 +489,9 @@
       <c r="M2">
         <v>71</v>
       </c>
+      <c r="N2" t="str">
+        <v>10 man days</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -527,6 +533,9 @@
       <c r="M3">
         <v>12</v>
       </c>
+      <c r="N3" t="str">
+        <v>120000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -568,6 +577,9 @@
       <c r="M4">
         <v>99</v>
       </c>
+      <c r="N4" t="str">
+        <v>450 man days</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -609,6 +621,9 @@
       <c r="M5">
         <v>95</v>
       </c>
+      <c r="N5" t="str">
+        <v>250000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -650,6 +665,9 @@
       <c r="M6">
         <v>100</v>
       </c>
+      <c r="N6" t="str">
+        <v>150000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -691,6 +709,9 @@
       <c r="M7">
         <v>21</v>
       </c>
+      <c r="N7" t="str">
+        <v>150 man days</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -732,6 +753,9 @@
       <c r="M8">
         <v>0</v>
       </c>
+      <c r="N8" t="str">
+        <v>80000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -773,6 +797,9 @@
       <c r="M9">
         <v>17</v>
       </c>
+      <c r="N9" t="str">
+        <v>200 man days</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -814,6 +841,9 @@
       <c r="M10">
         <v>95</v>
       </c>
+      <c r="N10" t="str">
+        <v>500000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -855,6 +885,9 @@
       <c r="M11">
         <v>95</v>
       </c>
+      <c r="N11" t="str">
+        <v>60000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -896,10 +929,13 @@
       <c r="M12">
         <v>19</v>
       </c>
+      <c r="N12" t="str">
+        <v>300 man days</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/database.xlsx
+++ b/database.xlsx
@@ -34,12 +34,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="d-mmm-yy"/>
-    <numFmt numFmtId="165" formatCode="d-mmmm-yy"/>
-    <numFmt numFmtId="166" formatCode="dd-mmmm-yy"/>
-    <numFmt numFmtId="167" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -403,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,7 +471,7 @@
         <v>Ananth</v>
       </c>
       <c r="I2" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
       <c r="J2" t="str">
         <v>delayed</v>
@@ -534,7 +530,7 @@
         <v>12</v>
       </c>
       <c r="N3" t="str">
-        <v>120000</v>
+        <v>48 man days</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +618,7 @@
         <v>95</v>
       </c>
       <c r="N5" t="str">
-        <v>250000</v>
+        <v>100 man days</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +662,7 @@
         <v>100</v>
       </c>
       <c r="N6" t="str">
-        <v>150000</v>
+        <v>60 man days</v>
       </c>
     </row>
     <row r="7">
@@ -754,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="str">
-        <v>80000</v>
+        <v>32 man days</v>
       </c>
     </row>
     <row r="9">
@@ -842,7 +838,7 @@
         <v>95</v>
       </c>
       <c r="N10" t="str">
-        <v>500000</v>
+        <v>200 man days</v>
       </c>
     </row>
     <row r="11">
@@ -886,7 +882,7 @@
         <v>95</v>
       </c>
       <c r="N11" t="str">
-        <v>60000</v>
+        <v>24 man days</v>
       </c>
     </row>
     <row r="12">
@@ -933,16 +929,464 @@
         <v>300 man days</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Shipping Bill End-to-End Automation</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Shipping Bill End-to-End Automation implementation and optimization.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F13">
+        <v>1500000</v>
+      </c>
+      <c r="G13">
+        <v>1500000</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Export logistics</v>
+      </c>
+      <c r="I13" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J13" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13" t="str">
+        <v>150 man days</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Auto Shipment Line License Linking</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Auto Shipment Line License Linking implementation and optimization.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="F14">
+        <v>2000000</v>
+      </c>
+      <c r="G14">
+        <v>1156000</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I14" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J14" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="L14" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="M14">
+        <v>68</v>
+      </c>
+      <c r="N14" t="str">
+        <v>120 man days</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Shipping Bill Checklist Verification Automation</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Shipping Bill Checklist Verification Automation implementation and optimization.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="F15">
+        <v>2500000</v>
+      </c>
+      <c r="G15">
+        <v>1338750</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Export logistics</v>
+      </c>
+      <c r="I15" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J15" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15">
+        <v>63</v>
+      </c>
+      <c r="N15" t="str">
+        <v>80 man days</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Addition Fields &amp; Controls in Intimation Session</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Addition Fields &amp; Controls in Intimation Session implementation and optimization.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="F16">
+        <v>1500000</v>
+      </c>
+      <c r="G16">
+        <v>535500</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I16" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J16" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="L16" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="M16">
+        <v>42</v>
+      </c>
+      <c r="N16" t="str">
+        <v>90 man days</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Freight Module Elimination</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Freight Module Elimination implementation and optimization.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="F17">
+        <v>2000000</v>
+      </c>
+      <c r="G17">
+        <v>1700000</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="I17" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J17" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="L17" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="str">
+        <v>110 man days</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Duplicate entry control in SB Session</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Duplicate entry control in SB Session implementation and optimization.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="F18">
+        <v>2500000</v>
+      </c>
+      <c r="G18">
+        <v>425000</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I18" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J18" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="L18" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M18">
+        <v>20</v>
+      </c>
+      <c r="N18" t="str">
+        <v>70 man days</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Complete rewiring of GST tax Invoice.</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Complete rewiring of GST tax Invoice. implementation and optimization.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="F19">
+        <v>1500000</v>
+      </c>
+      <c r="G19">
+        <v>637500</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I19" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J19" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19">
+        <v>50</v>
+      </c>
+      <c r="N19" t="str">
+        <v>100 man days</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Freight enquiry Agentic- RFQ, comparisoon, Nomination</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Freight enquiry Agentic- RFQ, comparisoon, Nomination implementation and optimization.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F20">
+        <v>2000000</v>
+      </c>
+      <c r="G20">
+        <v>1615000</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I20" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J20" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20">
+        <v>95</v>
+      </c>
+      <c r="N20" t="str">
+        <v>200 man days</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str" xml:space="preserve">
+        <v xml:space="preserve">ReMapping for logic for additional documents 
+ 1. CONTAINER BACK DECLARATION
+ 2. DHL SHIPPERS LETTER OF INSTRUCTION
+ 3. FEDEX SHIPPERS LETTER OF INSTRUCTION
+ 4. Digitally signed non-Haz declaration</v>
+      </c>
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">ReMapping for logic for additional documents 
+ 1. CONTAINER BACK DECLARATION
+ 2. DHL SHIPPERS LETTER OF INSTRUCTION
+ 3. FEDEX SHIPPERS LETTER OF INSTRUCTION
+ 4. Digitally signed non-Haz declaration implementation and optimization.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="F21">
+        <v>2500000</v>
+      </c>
+      <c r="G21">
+        <v>361250</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I21" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J21" t="str">
+        <v>on-track</v>
+      </c>
+      <c r="K21" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21">
+        <v>17</v>
+      </c>
+      <c r="N21" t="str">
+        <v>130 man days</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Shipping bill checklist - Creation</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Shipping bill checklist - Creation implementation and optimization.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="F22">
+        <v>1500000</v>
+      </c>
+      <c r="G22">
+        <v>1275000</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I22" t="str">
+        <v>exports</v>
+      </c>
+      <c r="J22" t="str">
+        <v>completed</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="L22" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22" t="str">
+        <v>60 man days</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5740,16 +6184,2436 @@
         <v>19</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>13</v>
+      </c>
+      <c r="B110" t="str">
+        <v>1</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Feasibility</v>
+      </c>
+      <c r="D110" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E110" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F110" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="G110" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="H110" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I110" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>13</v>
+      </c>
+      <c r="B111" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C111" t="str">
+        <v>SRF</v>
+      </c>
+      <c r="D111" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="E111" t="str">
+        <v>2026-03-31</v>
+      </c>
+      <c r="F111" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="G111" t="str">
+        <v>2026-04-03</v>
+      </c>
+      <c r="H111" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I111" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J111">
+        <v>3</v>
+      </c>
+      <c r="K111" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L111" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M111" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N111">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>13</v>
+      </c>
+      <c r="B112" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Development in Test server</v>
+      </c>
+      <c r="D112" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="E112" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="F112" t="str">
+        <v>2026-04-04</v>
+      </c>
+      <c r="G112" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="H112" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I112" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>13</v>
+      </c>
+      <c r="B113" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="C113" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D113" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="F113" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="G113" t="str">
+        <v>2026-04-28</v>
+      </c>
+      <c r="H113" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I113" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>13</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Development SRF</v>
+      </c>
+      <c r="D114" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E114" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F114" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="G114" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="H114" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I114" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>13</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C115" t="str">
+        <v>SRF Preparation</v>
+      </c>
+      <c r="D115" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E115" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="F115" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="G115" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I115" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>13</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C116" t="str">
+        <v>SRF Raised &amp; Approved</v>
+      </c>
+      <c r="D116" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F116" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="G116" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="H116" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I116" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>13</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2.3</v>
+      </c>
+      <c r="C117" t="str">
+        <v>SRF CCB Approval &amp; Attach in system</v>
+      </c>
+      <c r="D117" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F117" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="G117" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I117" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="K117" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L117" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M117" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N117">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>13</v>
+      </c>
+      <c r="B118" t="str">
+        <v>3</v>
+      </c>
+      <c r="C118" t="str">
+        <v>FSD</v>
+      </c>
+      <c r="D118" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="F118" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="G118" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="H118" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I118" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>13</v>
+      </c>
+      <c r="B119" t="str">
+        <v>3.1</v>
+      </c>
+      <c r="C119" t="str">
+        <v>FSD Preparation</v>
+      </c>
+      <c r="D119" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E119" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F119" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="G119" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="H119" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I119" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>13</v>
+      </c>
+      <c r="B120" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="C120" t="str">
+        <v>FSD Approval</v>
+      </c>
+      <c r="D120" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="E120" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="F120" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="G120" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="H120" t="str">
+        <v>Charit Exp Logis</v>
+      </c>
+      <c r="I120" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L120" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M120" t="str">
+        <v>Charit Exp Logis</v>
+      </c>
+      <c r="N120">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>13</v>
+      </c>
+      <c r="B121" t="str">
+        <v>4</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Infor Developmet</v>
+      </c>
+      <c r="D121" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F121" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="G121" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="H121" t="str">
+        <v>GITL User</v>
+      </c>
+      <c r="I121" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J121">
+        <v>4</v>
+      </c>
+      <c r="K121" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L121" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M121" t="str">
+        <v>GITL User</v>
+      </c>
+      <c r="N121">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>13</v>
+      </c>
+      <c r="B122" t="str">
+        <v>5</v>
+      </c>
+      <c r="C122" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D122" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-06-17</v>
+      </c>
+      <c r="F122" t="str">
+        <v>2026-06-17</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I122" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>13</v>
+      </c>
+      <c r="B123" t="str">
+        <v>6</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Live Loading</v>
+      </c>
+      <c r="D123" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-06-22</v>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I123" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>14</v>
+      </c>
+      <c r="B124" t="str">
+        <v>1</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Process Mapping</v>
+      </c>
+      <c r="D124" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="F124" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I124" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J124">
+        <v>9</v>
+      </c>
+      <c r="K124" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L124" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M124" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N124">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>14</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Script Developement</v>
+      </c>
+      <c r="D125" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="F125" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I125" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J125">
+        <v>3</v>
+      </c>
+      <c r="K125" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L125" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M125" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N125">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>14</v>
+      </c>
+      <c r="B126" t="str">
+        <v>3</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Script testing</v>
+      </c>
+      <c r="D126" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v>Export logistics</v>
+      </c>
+      <c r="I126" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>15</v>
+      </c>
+      <c r="B127" t="str">
+        <v>1</v>
+      </c>
+      <c r="C127" t="str">
+        <v>CRS</v>
+      </c>
+      <c r="D127" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="F127" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="G127" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I127" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>15</v>
+      </c>
+      <c r="B128" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Mapping &amp; Upload</v>
+      </c>
+      <c r="D128" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F128" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="G128" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I128" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>15</v>
+      </c>
+      <c r="B129" t="str">
+        <v>1.1.1</v>
+      </c>
+      <c r="C129" t="str">
+        <v>SRF Preparation</v>
+      </c>
+      <c r="D129" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="F129" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="G129" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="H129" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I129" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>15</v>
+      </c>
+      <c r="B130" t="str">
+        <v>1.1.2</v>
+      </c>
+      <c r="C130" t="str">
+        <v>SRf Uploaded</v>
+      </c>
+      <c r="D130" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="F130" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="G130" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I130" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>15</v>
+      </c>
+      <c r="B131" t="str">
+        <v>1.1.3</v>
+      </c>
+      <c r="C131" t="str">
+        <v>SRF Approval</v>
+      </c>
+      <c r="D131" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F131" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="G131" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I131" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>15</v>
+      </c>
+      <c r="B132" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="C132" t="str">
+        <v>CCB Approval</v>
+      </c>
+      <c r="D132" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E132" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F132" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G132" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="H132" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I132" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>15</v>
+      </c>
+      <c r="B133" t="str">
+        <v>1.2.1</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Received for CCB</v>
+      </c>
+      <c r="D133" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E133" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="F133" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G133" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I133" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>15</v>
+      </c>
+      <c r="B134" t="str">
+        <v>1.2.2</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Send for CCB Approval</v>
+      </c>
+      <c r="D134" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="E134" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="F134" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="G134" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I134" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>15</v>
+      </c>
+      <c r="B135" t="str">
+        <v>1.2.3</v>
+      </c>
+      <c r="C135" t="str">
+        <v>CCB Received</v>
+      </c>
+      <c r="D135" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="E135" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F135" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="G135" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="H135" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I135" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>15</v>
+      </c>
+      <c r="B136" t="str">
+        <v>1.2.4</v>
+      </c>
+      <c r="C136" t="str">
+        <v>CCB Attached to SRF</v>
+      </c>
+      <c r="D136" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E136" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F136" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="G136" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="H136" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I136" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>15</v>
+      </c>
+      <c r="B137" t="str">
+        <v>2</v>
+      </c>
+      <c r="C137" t="str">
+        <v>FSD</v>
+      </c>
+      <c r="D137" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E137" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F137" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="G137" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="H137" t="str">
+        <v>GIT Mehrshad</v>
+      </c>
+      <c r="I137" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>15</v>
+      </c>
+      <c r="B138" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C138" t="str">
+        <v>FSD Preparation</v>
+      </c>
+      <c r="D138" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E138" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="F138" t="str">
+        <v>2026-05-22</v>
+      </c>
+      <c r="G138" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="H138" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I138" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>15</v>
+      </c>
+      <c r="B139" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C139" t="str">
+        <v>FSD Approval</v>
+      </c>
+      <c r="D139" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E139" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F139" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="G139" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="H139" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I139" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J139">
+        <v>6</v>
+      </c>
+      <c r="K139" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L139" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M139" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N139">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>15</v>
+      </c>
+      <c r="B140" t="str">
+        <v>3</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Infor Developmet</v>
+      </c>
+      <c r="D140" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E140" t="str">
+        <v>2026-08-25</v>
+      </c>
+      <c r="F140" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+      <c r="H140" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I140" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>15</v>
+      </c>
+      <c r="B141" t="str">
+        <v>4</v>
+      </c>
+      <c r="C141" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I141" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>15</v>
+      </c>
+      <c r="B142" t="str">
+        <v>5</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Live Loading</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I142" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
+        <v/>
+      </c>
+      <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>16</v>
+      </c>
+      <c r="B143" t="str">
+        <v>1</v>
+      </c>
+      <c r="C143" t="str">
+        <v>CRS</v>
+      </c>
+      <c r="D143" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E143" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="F143" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G143" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="H143" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="I143" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>16</v>
+      </c>
+      <c r="B144" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Mapping &amp; Upload</v>
+      </c>
+      <c r="D144" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E144" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="F144" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="I144" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>16</v>
+      </c>
+      <c r="B145" t="str">
+        <v>1.1.1</v>
+      </c>
+      <c r="C145" t="str">
+        <v>CRS Preparation</v>
+      </c>
+      <c r="D145" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E145" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="I145" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J145">
+        <v>19</v>
+      </c>
+      <c r="K145" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M145" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>16</v>
+      </c>
+      <c r="B146" t="str">
+        <v>1.1.2</v>
+      </c>
+      <c r="C146" t="str">
+        <v>CRS Raised &amp; Approved</v>
+      </c>
+      <c r="D146" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I146" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J146">
+        <v>15</v>
+      </c>
+      <c r="K146" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M146" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>17</v>
+      </c>
+      <c r="B147" t="str">
+        <v>1</v>
+      </c>
+      <c r="C147" t="str">
+        <v>SRF</v>
+      </c>
+      <c r="D147" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E147" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="F147" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="G147" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="H147" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I147" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>17</v>
+      </c>
+      <c r="B148" t="str">
+        <v>1.1</v>
+      </c>
+      <c r="C148" t="str">
+        <v>SRF Preparation</v>
+      </c>
+      <c r="D148" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E148" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F148" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="G148" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="H148" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I148" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>17</v>
+      </c>
+      <c r="B149" t="str">
+        <v>1.2</v>
+      </c>
+      <c r="C149" t="str">
+        <v>SRF Raised &amp; Approved</v>
+      </c>
+      <c r="D149" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="F149" t="str">
+        <v>2026-05-18</v>
+      </c>
+      <c r="G149" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="H149" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I149" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J149">
+        <v>14</v>
+      </c>
+      <c r="K149" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M149" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N149">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>17</v>
+      </c>
+      <c r="B150" t="str">
+        <v>1.3</v>
+      </c>
+      <c r="C150" t="str">
+        <v>SRF CCB Approval &amp; Attach in system</v>
+      </c>
+      <c r="D150" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="E150" t="str">
+        <v>2026-05-26</v>
+      </c>
+      <c r="F150" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I150" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J150">
+        <v>18</v>
+      </c>
+      <c r="K150" t="str">
+        <v>Pending for CCB. Emailed to Manoj sir with reasons</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M150" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N150">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>17</v>
+      </c>
+      <c r="B151" t="str">
+        <v>2</v>
+      </c>
+      <c r="C151" t="str">
+        <v>FSD</v>
+      </c>
+      <c r="D151" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I151" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>17</v>
+      </c>
+      <c r="B152" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="C152" t="str">
+        <v>FSD Preparation</v>
+      </c>
+      <c r="D152" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E152" t="str">
+        <v>2026-05-29</v>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I152" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J152">
+        <v>15</v>
+      </c>
+      <c r="K152" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M152" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>17</v>
+      </c>
+      <c r="B153" t="str">
+        <v>2.2</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FSD Approval</v>
+      </c>
+      <c r="D153" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I153" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J153">
+        <v>11</v>
+      </c>
+      <c r="K153" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M153" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>17</v>
+      </c>
+      <c r="B154" t="str">
+        <v>3</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Infor Developmet</v>
+      </c>
+      <c r="D154" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E154" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I154" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J154">
+        <v>8</v>
+      </c>
+      <c r="K154" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M154" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>17</v>
+      </c>
+      <c r="B155" t="str">
+        <v>4</v>
+      </c>
+      <c r="C155" t="str">
+        <v>UAT</v>
+      </c>
+      <c r="D155" t="str">
+        <v>2026-06-08</v>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="I155" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M155" t="str">
+        <v>Charit</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>17</v>
+      </c>
+      <c r="B156" t="str">
+        <v>5</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Live</v>
+      </c>
+      <c r="D156" t="str">
+        <v>2026-06-13</v>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I156" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
+      <c r="L156" t="str">
+        <v/>
+      </c>
+      <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>17</v>
+      </c>
+      <c r="B157" t="str">
+        <v>5.1</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Live Loading</v>
+      </c>
+      <c r="D157" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E157" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="I157" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J157">
+        <v>31</v>
+      </c>
+      <c r="K157" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L157" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M157" t="str">
+        <v>GITL</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>17</v>
+      </c>
+      <c r="B158" t="str">
+        <v>5.2</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Live Testing &amp; Final Confirmation</v>
+      </c>
+      <c r="D158" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E158" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v>Us &amp; GITL</v>
+      </c>
+      <c r="I158" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J158">
+        <v>29</v>
+      </c>
+      <c r="K158" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M158" t="str">
+        <v>Us &amp; GITL</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>18</v>
+      </c>
+      <c r="B159" t="str">
+        <v>1</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Mapping</v>
+      </c>
+      <c r="D159" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="F159" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="G159" t="str">
+        <v>2026-03-30</v>
+      </c>
+      <c r="H159" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I159" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
+      <c r="L159" t="str">
+        <v/>
+      </c>
+      <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>18</v>
+      </c>
+      <c r="B160" t="str">
+        <v>2</v>
+      </c>
+      <c r="C160" t="str">
+        <v>SRF</v>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I160" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
+      <c r="L160" t="str">
+        <v/>
+      </c>
+      <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>19</v>
+      </c>
+      <c r="B161" t="str">
+        <v>1</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Mapping Agentic</v>
+      </c>
+      <c r="D161" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="E161" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="F161" t="str">
+        <v>2026-05-05</v>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I161" t="str">
+        <v>delayed</v>
+      </c>
+      <c r="J161">
+        <v>14</v>
+      </c>
+      <c r="K161" t="str">
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="L161" t="str">
+        <v>Pushed back downstream task completions.</v>
+      </c>
+      <c r="M161" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="N161">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>20</v>
+      </c>
+      <c r="B162" t="str">
+        <v>1</v>
+      </c>
+      <c r="C162" t="str">
+        <v>SRF FSD</v>
+      </c>
+      <c r="D162" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-06-19</v>
+      </c>
+      <c r="F162" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I162" t="str">
+        <v>in-progress</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
+      <c r="L162" t="str">
+        <v/>
+      </c>
+      <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>20</v>
+      </c>
+      <c r="B163" t="str">
+        <v>2</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Live Loading</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v/>
+      </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I163" t="str">
+        <v>not-started</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
+      <c r="L163" t="str">
+        <v/>
+      </c>
+      <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>21</v>
+      </c>
+      <c r="B164" t="str">
+        <v>1</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Mapping</v>
+      </c>
+      <c r="D164" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="F164" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="G164" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="H164" t="str">
+        <v>Mehrshad</v>
+      </c>
+      <c r="I164" t="str">
+        <v>completed</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
+      <c r="L164" t="str">
+        <v/>
+      </c>
+      <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N164"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5776,7 +8640,7 @@
         <v>Senior Solutions Architect</v>
       </c>
       <c r="D2" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="3">
@@ -5860,7 +8724,7 @@
         <v>Core Technical Lead Team</v>
       </c>
       <c r="D8" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="9">
@@ -5874,7 +8738,7 @@
         <v>Risk &amp; Compliance Sponsor</v>
       </c>
       <c r="D9" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="10">
@@ -5888,7 +8752,7 @@
         <v>Joint Implementation Partners</v>
       </c>
       <c r="D10" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="11">
@@ -5902,7 +8766,7 @@
         <v>Offshore Team Lead</v>
       </c>
       <c r="D11" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="12">
@@ -5916,7 +8780,7 @@
         <v>Digital Transformation Manager</v>
       </c>
       <c r="D12" t="str">
-        <v>corporate procurement digital</v>
+        <v>corp proc digital</v>
       </c>
     </row>
     <row r="13">
@@ -6031,9 +8895,79 @@
         <v>imports</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>tm20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Export logistics</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Export Logistics Operations Lead</v>
+      </c>
+      <c r="D21" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>tm21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Rama Sir</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Senior Logistics sponsor</v>
+      </c>
+      <c r="D22" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>tm22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Charit Exp Logis</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Logistics Systems Engineer</v>
+      </c>
+      <c r="D23" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>tm23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>GITL User</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Operations Specialist</v>
+      </c>
+      <c r="D24" t="str">
+        <v>exports</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>tm24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>GIT Mehrshad</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Business Integrator</v>
+      </c>
+      <c r="D25" t="str">
+        <v>exports</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -1,11 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011" filterPrivacy="true"/>
   <sheets>
     <sheet name="Project Details" sheetId="1" r:id="rId1"/>
     <sheet name="Tasks" sheetId="2" r:id="rId2"/>
     <sheet name="TeamMembers" sheetId="3" r:id="rId3"/>
+    <sheet name="SRF Summary" sheetId="4" r:id="rId4"/>
+    <sheet name="Kaizen" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -34,8 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="₹#,##,##0"/>
+    <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -399,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:K22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,30 +422,21 @@
         <v>Project Planned End Date</v>
       </c>
       <c r="F1" t="str">
-        <v>Project Budget</v>
+        <v>Project Spent</v>
       </c>
       <c r="G1" t="str">
-        <v>Project Spent</v>
+        <v>Project Manager</v>
       </c>
       <c r="H1" t="str">
-        <v>Project Manager</v>
+        <v>Department</v>
       </c>
       <c r="I1" t="str">
-        <v>Department</v>
+        <v>Project Actual Start Date</v>
       </c>
       <c r="J1" t="str">
-        <v>Project Status</v>
+        <v>Project Actual End Date</v>
       </c>
       <c r="K1" t="str">
-        <v>Project Actual Start Date</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Project Actual End Date</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Project Progress</v>
-      </c>
-      <c r="N1" t="str">
         <v>Project Benefits</v>
       </c>
     </row>
@@ -462,30 +457,21 @@
         <v>2026-05-22</v>
       </c>
       <c r="F2">
-        <v>3500000</v>
-      </c>
-      <c r="G2">
-        <v>2885750</v>
+        <v>62500</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Ananth</v>
       </c>
       <c r="H2" t="str">
-        <v>Ananth</v>
+        <v>corp proc digital</v>
       </c>
       <c r="I2" t="str">
-        <v>corp proc digital</v>
+        <v>2026-02-11</v>
       </c>
       <c r="J2" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2">
-        <v>71</v>
-      </c>
-      <c r="N2" t="str">
         <v>10 man days</v>
       </c>
     </row>
@@ -506,30 +492,21 @@
         <v>2026-09-16</v>
       </c>
       <c r="F3">
-        <v>4500000</v>
-      </c>
-      <c r="G3">
-        <v>612000</v>
+        <v>100000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Mehrshad Nava</v>
       </c>
       <c r="H3" t="str">
-        <v>Mehrshad Nava</v>
+        <v>finance</v>
       </c>
       <c r="I3" t="str">
-        <v>finance</v>
+        <v>2026-04-15</v>
       </c>
       <c r="J3" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3">
-        <v>12</v>
-      </c>
-      <c r="N3" t="str">
         <v>48 man days</v>
       </c>
     </row>
@@ -550,30 +527,21 @@
         <v>2026-04-29</v>
       </c>
       <c r="F4">
-        <v>2500000</v>
-      </c>
-      <c r="G4">
-        <v>2103750</v>
+        <v>125000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Ivan</v>
       </c>
       <c r="H4" t="str">
-        <v>Ivan</v>
+        <v>exports</v>
       </c>
       <c r="I4" t="str">
-        <v>exports</v>
+        <v>2026-02-11</v>
       </c>
       <c r="J4" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4">
-        <v>99</v>
-      </c>
-      <c r="N4" t="str">
         <v>450 man days</v>
       </c>
     </row>
@@ -594,30 +562,21 @@
         <v>2026-06-12</v>
       </c>
       <c r="F5">
-        <v>3500000</v>
-      </c>
-      <c r="G5">
-        <v>2945250</v>
+        <v>50000</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Ananth</v>
       </c>
       <c r="H5" t="str">
-        <v>Ananth</v>
+        <v>finance</v>
       </c>
       <c r="I5" t="str">
-        <v>finance</v>
+        <v>2026-02-11</v>
       </c>
       <c r="J5" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5">
-        <v>95</v>
-      </c>
-      <c r="N5" t="str">
         <v>100 man days</v>
       </c>
     </row>
@@ -638,30 +597,21 @@
         <v>2026-06-02</v>
       </c>
       <c r="F6">
-        <v>4500000</v>
-      </c>
-      <c r="G6">
         <v>3825000</v>
       </c>
+      <c r="G6" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H6" t="str">
-        <v>Charit</v>
+        <v>banking</v>
       </c>
       <c r="I6" t="str">
-        <v>banking</v>
+        <v>2026-05-04</v>
       </c>
       <c r="J6" t="str">
-        <v>completed</v>
+        <v>2026-06-02</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-05-04</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6" t="str">
         <v>60 man days</v>
       </c>
     </row>
@@ -682,30 +632,21 @@
         <v>2026-06-06</v>
       </c>
       <c r="F7">
-        <v>2500000</v>
-      </c>
-      <c r="G7">
         <v>680000</v>
       </c>
+      <c r="G7" t="str">
+        <v>Mehrshad</v>
+      </c>
       <c r="H7" t="str">
-        <v>Mehrshad</v>
+        <v>imports</v>
       </c>
       <c r="I7" t="str">
-        <v>imports</v>
+        <v>2026-04-29</v>
       </c>
       <c r="J7" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-29</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7">
-        <v>21</v>
-      </c>
-      <c r="N7" t="str">
         <v>150 man days</v>
       </c>
     </row>
@@ -726,30 +667,21 @@
         <v>2026-06-19</v>
       </c>
       <c r="F8">
-        <v>3500000</v>
-      </c>
-      <c r="G8">
         <v>0</v>
       </c>
+      <c r="G8" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H8" t="str">
-        <v>Charit</v>
+        <v>imports</v>
       </c>
       <c r="I8" t="str">
-        <v>imports</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="str">
         <v>32 man days</v>
       </c>
     </row>
@@ -770,30 +702,21 @@
         <v>2026-06-30</v>
       </c>
       <c r="F9">
-        <v>4500000</v>
-      </c>
-      <c r="G9">
         <v>1262250</v>
       </c>
+      <c r="G9" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H9" t="str">
-        <v>Charit</v>
+        <v>imports</v>
       </c>
       <c r="I9" t="str">
-        <v>imports</v>
+        <v>2026-03-03</v>
       </c>
       <c r="J9" t="str">
-        <v>completed</v>
+        <v>2026-06-30</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="L9" t="str">
-        <v>2026-06-30</v>
-      </c>
-      <c r="M9">
-        <v>17</v>
-      </c>
-      <c r="N9" t="str">
         <v>200 man days</v>
       </c>
     </row>
@@ -814,30 +737,21 @@
         <v>2026-06-30</v>
       </c>
       <c r="F10">
-        <v>2500000</v>
-      </c>
-      <c r="G10">
         <v>2018750</v>
       </c>
+      <c r="G10" t="str">
+        <v>Ivan &amp; Ananth</v>
+      </c>
       <c r="H10" t="str">
-        <v>Ivan &amp; Ananth</v>
+        <v>banking</v>
       </c>
       <c r="I10" t="str">
-        <v>banking</v>
+        <v>2026-06-04</v>
       </c>
       <c r="J10" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K10" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10">
-        <v>95</v>
-      </c>
-      <c r="N10" t="str">
         <v>200 man days</v>
       </c>
     </row>
@@ -858,30 +772,21 @@
         <v>2026-06-12</v>
       </c>
       <c r="F11">
-        <v>3500000</v>
-      </c>
-      <c r="G11">
         <v>2826250</v>
       </c>
+      <c r="G11" t="str">
+        <v>Ivan</v>
+      </c>
       <c r="H11" t="str">
-        <v>Ivan</v>
+        <v>it</v>
       </c>
       <c r="I11" t="str">
-        <v>it</v>
+        <v>2026-05-25</v>
       </c>
       <c r="J11" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K11" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11">
-        <v>95</v>
-      </c>
-      <c r="N11" t="str">
         <v>24 man days</v>
       </c>
     </row>
@@ -902,30 +807,21 @@
         <v>2026-06-30</v>
       </c>
       <c r="F12">
-        <v>4500000</v>
-      </c>
-      <c r="G12">
         <v>726750</v>
       </c>
+      <c r="G12" t="str">
+        <v>Ivan</v>
+      </c>
       <c r="H12" t="str">
-        <v>Ivan</v>
+        <v>steel</v>
       </c>
       <c r="I12" t="str">
-        <v>steel</v>
+        <v>2026-06-09</v>
       </c>
       <c r="J12" t="str">
-        <v>on-track</v>
+        <v/>
       </c>
       <c r="K12" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12">
-        <v>19</v>
-      </c>
-      <c r="N12" t="str">
         <v>300 man days</v>
       </c>
     </row>
@@ -948,28 +844,19 @@
       <c r="F13">
         <v>1500000</v>
       </c>
-      <c r="G13">
-        <v>1500000</v>
+      <c r="G13" t="str">
+        <v>Export logistics</v>
       </c>
       <c r="H13" t="str">
-        <v>Export logistics</v>
+        <v>exports</v>
       </c>
       <c r="I13" t="str">
-        <v>exports</v>
+        <v>2026-01-12</v>
       </c>
       <c r="J13" t="str">
-        <v>completed</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-01-12</v>
-      </c>
-      <c r="L13" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13" t="str">
         <v>150 man days</v>
       </c>
     </row>
@@ -990,30 +877,21 @@
         <v>2026-06-15</v>
       </c>
       <c r="F14">
-        <v>2000000</v>
-      </c>
-      <c r="G14">
         <v>1156000</v>
       </c>
+      <c r="G14" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H14" t="str">
-        <v>Charit</v>
+        <v>exports</v>
       </c>
       <c r="I14" t="str">
-        <v>exports</v>
+        <v>2026-03-11</v>
       </c>
       <c r="J14" t="str">
-        <v>completed</v>
+        <v>2026-06-22</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="L14" t="str">
-        <v>2026-06-22</v>
-      </c>
-      <c r="M14">
-        <v>68</v>
-      </c>
-      <c r="N14" t="str">
         <v>120 man days</v>
       </c>
     </row>
@@ -1034,30 +912,21 @@
         <v>2026-06-04</v>
       </c>
       <c r="F15">
-        <v>2500000</v>
-      </c>
-      <c r="G15">
         <v>1338750</v>
       </c>
+      <c r="G15" t="str">
+        <v>Export logistics</v>
+      </c>
       <c r="H15" t="str">
-        <v>Export logistics</v>
+        <v>exports</v>
       </c>
       <c r="I15" t="str">
-        <v>exports</v>
+        <v>2026-05-07</v>
       </c>
       <c r="J15" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K15" t="str">
-        <v>2026-05-07</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15">
-        <v>63</v>
-      </c>
-      <c r="N15" t="str">
         <v>80 man days</v>
       </c>
     </row>
@@ -1078,30 +947,21 @@
         <v>2026-07-31</v>
       </c>
       <c r="F16">
-        <v>1500000</v>
-      </c>
-      <c r="G16">
         <v>535500</v>
       </c>
+      <c r="G16" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H16" t="str">
-        <v>Charit</v>
+        <v>exports</v>
       </c>
       <c r="I16" t="str">
-        <v>exports</v>
+        <v>2026-05-11</v>
       </c>
       <c r="J16" t="str">
-        <v>completed</v>
+        <v>2026-07-31</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="L16" t="str">
-        <v>2026-07-31</v>
-      </c>
-      <c r="M16">
-        <v>42</v>
-      </c>
-      <c r="N16" t="str">
         <v>90 man days</v>
       </c>
     </row>
@@ -1122,30 +982,21 @@
         <v>2026-08-31</v>
       </c>
       <c r="F17">
-        <v>2000000</v>
-      </c>
-      <c r="G17">
         <v>1700000</v>
       </c>
+      <c r="G17" t="str">
+        <v>Rama Sir</v>
+      </c>
       <c r="H17" t="str">
-        <v>Rama Sir</v>
+        <v>exports</v>
       </c>
       <c r="I17" t="str">
-        <v>exports</v>
+        <v>2026-05-18</v>
       </c>
       <c r="J17" t="str">
-        <v>completed</v>
+        <v>2026-08-31</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-05-18</v>
-      </c>
-      <c r="L17" t="str">
-        <v>2026-08-31</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="str">
         <v>110 man days</v>
       </c>
     </row>
@@ -1166,30 +1017,21 @@
         <v>2026-06-15</v>
       </c>
       <c r="F18">
-        <v>2500000</v>
-      </c>
-      <c r="G18">
         <v>425000</v>
       </c>
+      <c r="G18" t="str">
+        <v>Charit</v>
+      </c>
       <c r="H18" t="str">
-        <v>Charit</v>
+        <v>exports</v>
       </c>
       <c r="I18" t="str">
-        <v>exports</v>
+        <v>2026-05-15</v>
       </c>
       <c r="J18" t="str">
-        <v>completed</v>
+        <v>2026-06-15</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="L18" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M18">
-        <v>20</v>
-      </c>
-      <c r="N18" t="str">
         <v>70 man days</v>
       </c>
     </row>
@@ -1210,30 +1052,21 @@
         <v>2026-03-30</v>
       </c>
       <c r="F19">
-        <v>1500000</v>
-      </c>
-      <c r="G19">
         <v>637500</v>
       </c>
+      <c r="G19" t="str">
+        <v>Mehrshad</v>
+      </c>
       <c r="H19" t="str">
-        <v>Mehrshad</v>
+        <v>exports</v>
       </c>
       <c r="I19" t="str">
-        <v>exports</v>
+        <v>2026-03-20</v>
       </c>
       <c r="J19" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K19" t="str">
-        <v>2026-03-20</v>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19">
-        <v>50</v>
-      </c>
-      <c r="N19" t="str">
         <v>100 man days</v>
       </c>
     </row>
@@ -1254,30 +1087,21 @@
         <v>2026-05-30</v>
       </c>
       <c r="F20">
-        <v>2000000</v>
-      </c>
-      <c r="G20">
         <v>1615000</v>
       </c>
+      <c r="G20" t="str">
+        <v>Mehrshad</v>
+      </c>
       <c r="H20" t="str">
-        <v>Mehrshad</v>
+        <v>exports</v>
       </c>
       <c r="I20" t="str">
-        <v>exports</v>
+        <v>2026-05-05</v>
       </c>
       <c r="J20" t="str">
-        <v>delayed</v>
+        <v/>
       </c>
       <c r="K20" t="str">
-        <v>2026-05-05</v>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20">
-        <v>95</v>
-      </c>
-      <c r="N20" t="str">
         <v>200 man days</v>
       </c>
     </row>
@@ -1306,30 +1130,21 @@
         <v>2026-06-19</v>
       </c>
       <c r="F21">
-        <v>2500000</v>
-      </c>
-      <c r="G21">
         <v>361250</v>
       </c>
+      <c r="G21" t="str">
+        <v>Mehrshad</v>
+      </c>
       <c r="H21" t="str">
-        <v>Mehrshad</v>
+        <v>exports</v>
       </c>
       <c r="I21" t="str">
-        <v>exports</v>
+        <v>2026-06-10</v>
       </c>
       <c r="J21" t="str">
-        <v>on-track</v>
+        <v/>
       </c>
       <c r="K21" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
-      <c r="M21">
-        <v>17</v>
-      </c>
-      <c r="N21" t="str">
         <v>130 man days</v>
       </c>
     </row>
@@ -1350,43 +1165,34 @@
         <v>2026-06-25</v>
       </c>
       <c r="F22">
-        <v>1500000</v>
-      </c>
-      <c r="G22">
         <v>1275000</v>
       </c>
+      <c r="G22" t="str">
+        <v>Mehrshad</v>
+      </c>
       <c r="H22" t="str">
-        <v>Mehrshad</v>
+        <v>exports</v>
       </c>
       <c r="I22" t="str">
-        <v>exports</v>
+        <v>2026-05-25</v>
       </c>
       <c r="J22" t="str">
-        <v>completed</v>
+        <v>2026-06-25</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="L22" t="str">
-        <v>2026-06-25</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22" t="str">
         <v>60 man days</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N164"/>
+  <dimension ref="A1:K164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1414,22 +1220,13 @@
         <v>Task Assignee</v>
       </c>
       <c r="I1" t="str">
-        <v>Task Status</v>
+        <v>Task Delay Reason</v>
       </c>
       <c r="J1" t="str">
-        <v>Task Days Delayed</v>
+        <v>Task Delay Impact</v>
       </c>
       <c r="K1" t="str">
-        <v>Task Delay Reason</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Task Delay Impact</v>
-      </c>
-      <c r="M1" t="str">
         <v>Task Delay Reported By</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Task Progress</v>
       </c>
     </row>
     <row r="2">
@@ -1458,22 +1255,13 @@
         <v>Ananth &amp; Ivan</v>
       </c>
       <c r="I2" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
       </c>
       <c r="K2" t="str">
         <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2">
-        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1502,22 +1290,13 @@
         <v>Ananth &amp; Ivan</v>
       </c>
       <c r="I3" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
       </c>
       <c r="K3" t="str">
         <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3">
-        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1546,22 +1325,13 @@
         <v>Ananth</v>
       </c>
       <c r="I4" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
       </c>
       <c r="K4" t="str">
         <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4">
-        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1590,22 +1360,13 @@
         <v>Ananth</v>
       </c>
       <c r="I5" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
       </c>
       <c r="K5" t="str">
         <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5">
-        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1634,22 +1395,13 @@
         <v>Ivan</v>
       </c>
       <c r="I6" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
       </c>
       <c r="K6" t="str">
         <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6">
-        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1678,22 +1430,13 @@
         <v>Ananth</v>
       </c>
       <c r="I7" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
       <c r="K7" t="str">
         <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
-      <c r="N7">
-        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1722,22 +1465,13 @@
         <v>RDC</v>
       </c>
       <c r="I8" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J8">
-        <v>22</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K8" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M8" t="str">
         <v>RDC</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1766,22 +1500,13 @@
         <v>Us &amp; GITL</v>
       </c>
       <c r="I9" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
       </c>
       <c r="K9" t="str">
         <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9">
-        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -1810,22 +1535,13 @@
         <v>Us &amp; GITL</v>
       </c>
       <c r="I10" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
       </c>
       <c r="K10" t="str">
         <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10">
-        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1854,22 +1570,13 @@
         <v>Us &amp; GITL</v>
       </c>
       <c r="I11" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
       </c>
       <c r="K11" t="str">
         <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11">
-        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1898,22 +1605,13 @@
         <v>Ananth</v>
       </c>
       <c r="I12" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
       </c>
       <c r="K12" t="str">
         <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12">
-        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1942,22 +1640,13 @@
         <v>Ananth</v>
       </c>
       <c r="I13" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
       </c>
       <c r="K13" t="str">
         <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13">
-        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1986,22 +1675,13 @@
         <v>GITL</v>
       </c>
       <c r="I14" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J14">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K14" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M14" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N14">
-        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -2030,22 +1710,13 @@
         <v>Us &amp; GITL</v>
       </c>
       <c r="I15" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
       </c>
       <c r="K15" t="str">
         <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15">
-        <v>98</v>
       </c>
     </row>
     <row r="16">
@@ -2074,22 +1745,13 @@
         <v>Ananth</v>
       </c>
       <c r="I16" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
       </c>
       <c r="K16" t="str">
         <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16">
-        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2118,22 +1780,13 @@
         <v>Ananth</v>
       </c>
       <c r="I17" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
       </c>
       <c r="K17" t="str">
         <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17">
-        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -2162,22 +1815,13 @@
         <v>GITL</v>
       </c>
       <c r="I18" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J18">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K18" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M18" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N18">
-        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -2206,22 +1850,13 @@
         <v>GITL</v>
       </c>
       <c r="I19" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
       </c>
       <c r="K19" t="str">
         <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2250,22 +1885,13 @@
         <v>GITL</v>
       </c>
       <c r="I20" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J20">
-        <v>31</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K20" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L20" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M20" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2294,22 +1920,13 @@
         <v>GITL</v>
       </c>
       <c r="I21" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J21">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K21" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L21" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M21" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2338,22 +1955,13 @@
         <v>GITL</v>
       </c>
       <c r="I22" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
       </c>
       <c r="K22" t="str">
         <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22">
-        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -2382,22 +1990,13 @@
         <v>GITL</v>
       </c>
       <c r="I23" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J23">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K23" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L23" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M23" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N23">
-        <v>95</v>
       </c>
     </row>
     <row r="24">
@@ -2426,22 +2025,13 @@
         <v>GITL</v>
       </c>
       <c r="I24" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
       </c>
       <c r="K24" t="str">
         <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24">
-        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -2470,22 +2060,13 @@
         <v>GITL</v>
       </c>
       <c r="I25" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J25">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K25" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L25" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M25" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N25">
-        <v>95</v>
       </c>
     </row>
     <row r="26">
@@ -2514,22 +2095,13 @@
         <v>GITL</v>
       </c>
       <c r="I26" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J26">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K26" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L26" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M26" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N26">
-        <v>95</v>
       </c>
     </row>
     <row r="27">
@@ -2558,22 +2130,13 @@
         <v>GITL</v>
       </c>
       <c r="I27" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J27">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K27" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L27" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M27" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N27">
-        <v>95</v>
       </c>
     </row>
     <row r="28">
@@ -2602,22 +2165,13 @@
         <v>GITL</v>
       </c>
       <c r="I28" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J28">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K28" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L28" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M28" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N28">
-        <v>95</v>
       </c>
     </row>
     <row r="29">
@@ -2646,22 +2200,13 @@
         <v>GITL</v>
       </c>
       <c r="I29" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J29">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K29" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L29" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M29" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N29">
-        <v>95</v>
       </c>
     </row>
     <row r="30">
@@ -2690,22 +2235,13 @@
         <v>GITL</v>
       </c>
       <c r="I30" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
       </c>
       <c r="K30" t="str">
         <v/>
-      </c>
-      <c r="L30" t="str">
-        <v/>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2734,22 +2270,13 @@
         <v>GITL</v>
       </c>
       <c r="I31" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J31">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K31" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L31" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M31" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2778,22 +2305,13 @@
         <v>GITL</v>
       </c>
       <c r="I32" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J32">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K32" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L32" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M32" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2822,22 +2340,13 @@
         <v>Digital</v>
       </c>
       <c r="I33" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
       </c>
       <c r="K33" t="str">
         <v/>
-      </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33">
-        <v>64</v>
       </c>
     </row>
     <row r="34">
@@ -2866,22 +2375,13 @@
         <v>Digital</v>
       </c>
       <c r="I34" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
       </c>
       <c r="K34" t="str">
         <v/>
-      </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-      <c r="N34">
-        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -2910,22 +2410,13 @@
         <v>Digital</v>
       </c>
       <c r="I35" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J35">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K35" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L35" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M35" t="str">
         <v>Digital</v>
-      </c>
-      <c r="N35">
-        <v>95</v>
       </c>
     </row>
     <row r="36">
@@ -2954,22 +2445,13 @@
         <v>Digital</v>
       </c>
       <c r="I36" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J36">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K36" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L36" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M36" t="str">
         <v>Digital</v>
-      </c>
-      <c r="N36">
-        <v>95</v>
       </c>
     </row>
     <row r="37">
@@ -2998,22 +2480,13 @@
         <v>Digital</v>
       </c>
       <c r="I37" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J37">
-        <v>36</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K37" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L37" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M37" t="str">
         <v>Digital</v>
-      </c>
-      <c r="N37">
-        <v>95</v>
       </c>
     </row>
     <row r="38">
@@ -3042,22 +2515,13 @@
         <v>Digital</v>
       </c>
       <c r="I38" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J38">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K38" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L38" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M38" t="str">
         <v>Digital</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3086,22 +2550,13 @@
         <v>Digital</v>
       </c>
       <c r="I39" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J39">
-        <v>22</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K39" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L39" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M39" t="str">
         <v>Digital</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3130,22 +2585,13 @@
         <v>Ananth</v>
       </c>
       <c r="I40" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J40">
-        <v>22</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K40" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L40" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M40" t="str">
         <v>Ananth</v>
-      </c>
-      <c r="N40">
-        <v>95</v>
       </c>
     </row>
     <row r="41">
@@ -3174,22 +2620,13 @@
         <v>Mehrshad Nava</v>
       </c>
       <c r="I41" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
       </c>
       <c r="K41" t="str">
         <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41">
-        <v>71</v>
       </c>
     </row>
     <row r="42">
@@ -3218,22 +2655,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I42" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J42">
-        <v>19</v>
+        <v>Metting set with Mikhil sir 30-06</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K42" t="str">
-        <v>Metting set with Mikhil sir 30-06</v>
-      </c>
-      <c r="L42" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M42" t="str">
         <v>Charit Mehrshad</v>
-      </c>
-      <c r="N42">
-        <v>95</v>
       </c>
     </row>
     <row r="43">
@@ -3262,22 +2690,13 @@
         <v>GITL / internal</v>
       </c>
       <c r="I43" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J43">
-        <v>19</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K43" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L43" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M43" t="str">
         <v>GITL / internal</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3306,22 +2725,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I44" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J44">
-        <v>19</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K44" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L44" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M44" t="str">
         <v>Charit Mehrshad</v>
-      </c>
-      <c r="N44">
-        <v>95</v>
       </c>
     </row>
     <row r="45">
@@ -3350,22 +2760,13 @@
         <v>Mehrshad Nava</v>
       </c>
       <c r="I45" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
       </c>
       <c r="K45" t="str">
         <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45">
-        <v>93</v>
       </c>
     </row>
     <row r="46">
@@ -3394,22 +2795,13 @@
         <v>Mehrshad Nava</v>
       </c>
       <c r="I46" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
       </c>
       <c r="K46" t="str">
         <v/>
-      </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
-      <c r="N46">
-        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -3438,22 +2830,13 @@
         <v>Mehrshad Nava</v>
       </c>
       <c r="I47" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
       </c>
       <c r="K47" t="str">
         <v/>
-      </c>
-      <c r="L47" t="str">
-        <v/>
-      </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
-      <c r="N47">
-        <v>100</v>
       </c>
     </row>
     <row r="48">
@@ -3482,22 +2865,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I48" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
       </c>
       <c r="K48" t="str">
         <v/>
-      </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
-      <c r="N48">
-        <v>79</v>
       </c>
     </row>
     <row r="49">
@@ -3526,22 +2900,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I49" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
       </c>
       <c r="K49" t="str">
         <v/>
-      </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49">
-        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3570,22 +2935,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I50" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J50">
-        <v>26</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K50" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L50" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M50" t="str">
         <v>Charit Mehrshad</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3614,22 +2970,13 @@
         <v>Charit Mehrshad</v>
       </c>
       <c r="I51" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J51">
-        <v>24</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K51" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L51" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M51" t="str">
         <v>Charit Mehrshad</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3658,22 +3005,13 @@
         <v>Digital GITL</v>
       </c>
       <c r="I52" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J52">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K52" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L52" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M52" t="str">
         <v>Digital GITL</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3702,22 +3040,13 @@
         <v>Digital GITL</v>
       </c>
       <c r="I53" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
       </c>
       <c r="K53" t="str">
         <v/>
-      </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
-      <c r="N53">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3746,22 +3075,13 @@
         <v>GITL</v>
       </c>
       <c r="I54" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
       </c>
       <c r="K54" t="str">
         <v/>
-      </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
-      <c r="N54">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3790,22 +3110,13 @@
         <v>Digital</v>
       </c>
       <c r="I55" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
       </c>
       <c r="K55" t="str">
         <v/>
-      </c>
-      <c r="L55" t="str">
-        <v/>
-      </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-      <c r="N55">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3834,22 +3145,13 @@
         <v>Digital</v>
       </c>
       <c r="I56" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
       </c>
       <c r="K56" t="str">
         <v/>
-      </c>
-      <c r="L56" t="str">
-        <v/>
-      </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56">
-        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3878,22 +3180,13 @@
         <v>Digital GITL</v>
       </c>
       <c r="I57" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
       </c>
       <c r="K57" t="str">
         <v/>
-      </c>
-      <c r="L57" t="str">
-        <v/>
-      </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-      <c r="N57">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3922,22 +3215,13 @@
         <v>Digital GITL</v>
       </c>
       <c r="I58" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
       </c>
       <c r="K58" t="str">
         <v/>
-      </c>
-      <c r="L58" t="str">
-        <v/>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58">
-        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3966,22 +3250,13 @@
         <v>Mehrshad Nava</v>
       </c>
       <c r="I59" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
       </c>
       <c r="K59" t="str">
         <v/>
-      </c>
-      <c r="L59" t="str">
-        <v/>
-      </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59">
-        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4010,22 +3285,13 @@
         <v>Ivan Charit</v>
       </c>
       <c r="I60" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
       </c>
       <c r="K60" t="str">
         <v/>
-      </c>
-      <c r="L60" t="str">
-        <v/>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60">
-        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -4054,22 +3320,13 @@
         <v>Ivan</v>
       </c>
       <c r="I61" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
       </c>
       <c r="K61" t="str">
         <v/>
-      </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
-      <c r="N61">
-        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -4098,22 +3355,13 @@
         <v>Ivan ananath</v>
       </c>
       <c r="I62" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
       </c>
       <c r="K62" t="str">
         <v/>
-      </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
-      <c r="N62">
-        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -4142,22 +3390,13 @@
         <v>Ivan ananath</v>
       </c>
       <c r="I63" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
       </c>
       <c r="K63" t="str">
         <v/>
-      </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63">
-        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -4186,22 +3425,13 @@
         <v>Ivan ananath</v>
       </c>
       <c r="I64" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v/>
       </c>
       <c r="K64" t="str">
         <v/>
-      </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64">
-        <v>100</v>
       </c>
     </row>
     <row r="65">
@@ -4230,22 +3460,13 @@
         <v>Ivan ananath</v>
       </c>
       <c r="I65" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J65">
-        <v>23</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K65" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L65" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M65" t="str">
         <v>Ivan ananath</v>
-      </c>
-      <c r="N65">
-        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -4274,22 +3495,13 @@
         <v>GITL</v>
       </c>
       <c r="I66" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J66">
-        <v>45</v>
+        <v>planned end date 5th june</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K66" t="str">
-        <v>planned end date 5th june</v>
-      </c>
-      <c r="L66" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M66" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N66">
-        <v>95</v>
       </c>
     </row>
     <row r="67">
@@ -4318,22 +3530,13 @@
         <v>Ananth</v>
       </c>
       <c r="I67" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v/>
       </c>
       <c r="K67" t="str">
         <v/>
-      </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67">
-        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -4362,22 +3565,13 @@
         <v>Ananth</v>
       </c>
       <c r="I68" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v/>
       </c>
       <c r="K68" t="str">
         <v/>
-      </c>
-      <c r="L68" t="str">
-        <v/>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68">
-        <v>100</v>
       </c>
     </row>
     <row r="69">
@@ -4406,22 +3600,13 @@
         <v>Ananth</v>
       </c>
       <c r="I69" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v/>
       </c>
       <c r="K69" t="str">
         <v/>
-      </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
-      <c r="N69">
-        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -4450,22 +3635,13 @@
         <v>Ananth</v>
       </c>
       <c r="I70" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v/>
       </c>
       <c r="K70" t="str">
         <v/>
-      </c>
-      <c r="L70" t="str">
-        <v/>
-      </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-      <c r="N70">
-        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -4494,22 +3670,13 @@
         <v>Ananth</v>
       </c>
       <c r="I71" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J71">
-        <v>2</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K71" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L71" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M71" t="str">
         <v>Ananth</v>
-      </c>
-      <c r="N71">
-        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -4538,22 +3705,13 @@
         <v>Ananth</v>
       </c>
       <c r="I72" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K72" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L72" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M72" t="str">
         <v>Ananth</v>
-      </c>
-      <c r="N72">
-        <v>95</v>
       </c>
     </row>
     <row r="73">
@@ -4582,22 +3740,13 @@
         <v>Ananth</v>
       </c>
       <c r="I73" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
       </c>
       <c r="K73" t="str">
         <v/>
-      </c>
-      <c r="L73" t="str">
-        <v/>
-      </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-      <c r="N73">
-        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -4626,22 +3775,13 @@
         <v>Ananth</v>
       </c>
       <c r="I74" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
       </c>
       <c r="K74" t="str">
         <v/>
-      </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74">
-        <v>67</v>
       </c>
     </row>
     <row r="75">
@@ -4670,22 +3810,13 @@
         <v>Ananth</v>
       </c>
       <c r="I75" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
       </c>
       <c r="K75" t="str">
         <v/>
-      </c>
-      <c r="L75" t="str">
-        <v/>
-      </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-      <c r="N75">
-        <v>100</v>
       </c>
     </row>
     <row r="76">
@@ -4714,22 +3845,13 @@
         <v>Ananth</v>
       </c>
       <c r="I76" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
       </c>
       <c r="K76" t="str">
         <v/>
-      </c>
-      <c r="L76" t="str">
-        <v/>
-      </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
-      <c r="N76">
-        <v>100</v>
       </c>
     </row>
     <row r="77">
@@ -4758,22 +3880,13 @@
         <v>Ananth</v>
       </c>
       <c r="I77" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J77">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K77" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L77" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M77" t="str">
         <v>Ananth</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4802,22 +3915,13 @@
         <v>Charit &amp; Vaishanvi</v>
       </c>
       <c r="I78" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
       </c>
       <c r="K78" t="str">
         <v/>
-      </c>
-      <c r="L78" t="str">
-        <v/>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78">
-        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -4846,22 +3950,13 @@
         <v>Charit</v>
       </c>
       <c r="I79" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J79" t="str">
+        <v/>
       </c>
       <c r="K79" t="str">
         <v/>
-      </c>
-      <c r="L79" t="str">
-        <v/>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79">
-        <v>100</v>
       </c>
     </row>
     <row r="80">
@@ -4890,22 +3985,13 @@
         <v>Charit</v>
       </c>
       <c r="I80" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J80">
-        <v>2</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K80" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L80" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M80" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N80">
-        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -4934,22 +4020,13 @@
         <v>Charit &amp; Vaishanvi</v>
       </c>
       <c r="I81" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J81">
-        <v>5</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K81" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L81" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M81" t="str">
         <v>Charit &amp; Vaishanvi</v>
-      </c>
-      <c r="N81">
-        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -4978,22 +4055,13 @@
         <v>Charit</v>
       </c>
       <c r="I82" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J82">
-        <v>3</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K82" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L82" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M82" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N82">
-        <v>100</v>
       </c>
     </row>
     <row r="83">
@@ -5022,22 +4090,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I83" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J83">
-        <v>34</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K83" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L83" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M83" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N83">
-        <v>95</v>
       </c>
     </row>
     <row r="84">
@@ -5066,22 +4125,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I84" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v/>
       </c>
       <c r="K84" t="str">
         <v/>
-      </c>
-      <c r="L84" t="str">
-        <v/>
-      </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
-      <c r="N84">
-        <v>32</v>
       </c>
     </row>
     <row r="85">
@@ -5110,22 +4160,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I85" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J85">
-        <v>34</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K85" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L85" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M85" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N85">
-        <v>95</v>
       </c>
     </row>
     <row r="86">
@@ -5154,22 +4195,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I86" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J86">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K86" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L86" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M86" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5198,22 +4230,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I87" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J87">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K87" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L87" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M87" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5242,22 +4265,13 @@
         <v>Charit</v>
       </c>
       <c r="I88" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J88">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K88" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L88" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M88" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5286,22 +4300,13 @@
         <v>Charit</v>
       </c>
       <c r="I89" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J89">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J89" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K89" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L89" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M89" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5330,22 +4335,13 @@
         <v>Charit</v>
       </c>
       <c r="I90" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J90">
-        <v>8</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K90" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L90" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M90" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5374,22 +4370,13 @@
         <v>Charit</v>
       </c>
       <c r="I91" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J91">
-        <v>7</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K91" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L91" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M91" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5418,22 +4405,13 @@
         <v>Charit</v>
       </c>
       <c r="I92" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J92">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
       </c>
       <c r="K92" t="str">
         <v/>
-      </c>
-      <c r="L92" t="str">
-        <v/>
-      </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
-      <c r="N92">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5462,22 +4440,13 @@
         <v>Charit</v>
       </c>
       <c r="I93" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J93" t="str">
+        <v/>
       </c>
       <c r="K93" t="str">
         <v/>
-      </c>
-      <c r="L93" t="str">
-        <v/>
-      </c>
-      <c r="M93" t="str">
-        <v/>
-      </c>
-      <c r="N93">
-        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5506,22 +4475,13 @@
         <v>Benefits, Division, Purchase Team</v>
       </c>
       <c r="I94" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J94">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
       </c>
       <c r="K94" t="str">
         <v/>
-      </c>
-      <c r="L94" t="str">
-        <v/>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94">
-        <v>100</v>
       </c>
     </row>
     <row r="95">
@@ -5550,22 +4510,13 @@
         <v>Charit</v>
       </c>
       <c r="I95" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
       </c>
       <c r="K95" t="str">
         <v/>
-      </c>
-      <c r="L95" t="str">
-        <v/>
-      </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
-      <c r="N95">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5594,22 +4545,13 @@
         <v>Charit</v>
       </c>
       <c r="I96" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J96">
-        <v>8</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K96" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L96" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M96" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5638,22 +4580,13 @@
         <v>Charit</v>
       </c>
       <c r="I97" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J97">
-        <v>4</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K97" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L97" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M97" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5682,22 +4615,13 @@
         <v>Charit</v>
       </c>
       <c r="I98" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J98">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K98" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L98" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M98" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5726,22 +4650,13 @@
         <v>GITL</v>
       </c>
       <c r="I99" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J99">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
       </c>
       <c r="K99" t="str">
         <v/>
-      </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
-      <c r="M99" t="str">
-        <v/>
-      </c>
-      <c r="N99">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5770,22 +4685,13 @@
         <v>GITL</v>
       </c>
       <c r="I100" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J100">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
       </c>
       <c r="K100" t="str">
         <v/>
-      </c>
-      <c r="L100" t="str">
-        <v/>
-      </c>
-      <c r="M100" t="str">
-        <v/>
-      </c>
-      <c r="N100">
-        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5814,22 +4720,13 @@
         <v>Charit</v>
       </c>
       <c r="I101" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
       </c>
       <c r="K101" t="str">
         <v/>
-      </c>
-      <c r="L101" t="str">
-        <v/>
-      </c>
-      <c r="M101" t="str">
-        <v/>
-      </c>
-      <c r="N101">
-        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5858,22 +4755,13 @@
         <v>GITL</v>
       </c>
       <c r="I102" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
       </c>
       <c r="K102" t="str">
         <v/>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
-      <c r="N102">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5902,22 +4790,13 @@
         <v>ALL</v>
       </c>
       <c r="I103" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
       </c>
       <c r="K103" t="str">
         <v/>
-      </c>
-      <c r="L103" t="str">
-        <v/>
-      </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
-      <c r="N103">
-        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5946,22 +4825,13 @@
         <v>GITL</v>
       </c>
       <c r="I104" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
       </c>
       <c r="K104" t="str">
         <v/>
-      </c>
-      <c r="L104" t="str">
-        <v/>
-      </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
-      <c r="N104">
-        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5990,22 +4860,13 @@
         <v>Ivan &amp; Ananth</v>
       </c>
       <c r="I105" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J105">
-        <v>3</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K105" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L105" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M105" t="str">
         <v>Ivan &amp; Ananth</v>
-      </c>
-      <c r="N105">
-        <v>95</v>
       </c>
     </row>
     <row r="106">
@@ -6034,22 +4895,13 @@
         <v>Ivan</v>
       </c>
       <c r="I106" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J106">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K106" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L106" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M106" t="str">
         <v>Ivan</v>
-      </c>
-      <c r="N106">
-        <v>95</v>
       </c>
     </row>
     <row r="107">
@@ -6078,22 +4930,13 @@
         <v>Ivan</v>
       </c>
       <c r="I107" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J107">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
       </c>
       <c r="K107" t="str">
         <v/>
-      </c>
-      <c r="L107" t="str">
-        <v/>
-      </c>
-      <c r="M107" t="str">
-        <v/>
-      </c>
-      <c r="N107">
-        <v>19</v>
       </c>
     </row>
     <row r="108">
@@ -6122,22 +4965,13 @@
         <v>Ivan</v>
       </c>
       <c r="I108" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J108">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
       </c>
       <c r="K108" t="str">
         <v/>
-      </c>
-      <c r="L108" t="str">
-        <v/>
-      </c>
-      <c r="M108" t="str">
-        <v/>
-      </c>
-      <c r="N108">
-        <v>19</v>
       </c>
     </row>
     <row r="109">
@@ -6166,22 +5000,13 @@
         <v>Ananth</v>
       </c>
       <c r="I109" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J109">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
       </c>
       <c r="K109" t="str">
         <v/>
-      </c>
-      <c r="L109" t="str">
-        <v/>
-      </c>
-      <c r="M109" t="str">
-        <v/>
-      </c>
-      <c r="N109">
-        <v>19</v>
       </c>
     </row>
     <row r="110">
@@ -6210,22 +5035,13 @@
         <v>Charit</v>
       </c>
       <c r="I110" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J110">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
       </c>
       <c r="K110" t="str">
         <v/>
-      </c>
-      <c r="L110" t="str">
-        <v/>
-      </c>
-      <c r="M110" t="str">
-        <v/>
-      </c>
-      <c r="N110">
-        <v>100</v>
       </c>
     </row>
     <row r="111">
@@ -6254,22 +5070,13 @@
         <v>Charit</v>
       </c>
       <c r="I111" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J111">
-        <v>3</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J111" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K111" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L111" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M111" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N111">
-        <v>100</v>
       </c>
     </row>
     <row r="112">
@@ -6298,22 +5105,13 @@
         <v>GITL</v>
       </c>
       <c r="I112" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
       </c>
       <c r="K112" t="str">
         <v/>
-      </c>
-      <c r="L112" t="str">
-        <v/>
-      </c>
-      <c r="M112" t="str">
-        <v/>
-      </c>
-      <c r="N112">
-        <v>100</v>
       </c>
     </row>
     <row r="113">
@@ -6342,22 +5140,13 @@
         <v>Charit</v>
       </c>
       <c r="I113" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
       </c>
       <c r="K113" t="str">
         <v/>
-      </c>
-      <c r="L113" t="str">
-        <v/>
-      </c>
-      <c r="M113" t="str">
-        <v/>
-      </c>
-      <c r="N113">
-        <v>100</v>
       </c>
     </row>
     <row r="114">
@@ -6386,22 +5175,13 @@
         <v>Charit</v>
       </c>
       <c r="I114" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
       </c>
       <c r="K114" t="str">
         <v/>
-      </c>
-      <c r="L114" t="str">
-        <v/>
-      </c>
-      <c r="M114" t="str">
-        <v/>
-      </c>
-      <c r="N114">
-        <v>100</v>
       </c>
     </row>
     <row r="115">
@@ -6430,22 +5210,13 @@
         <v>Charit</v>
       </c>
       <c r="I115" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
       </c>
       <c r="K115" t="str">
         <v/>
-      </c>
-      <c r="L115" t="str">
-        <v/>
-      </c>
-      <c r="M115" t="str">
-        <v/>
-      </c>
-      <c r="N115">
-        <v>100</v>
       </c>
     </row>
     <row r="116">
@@ -6474,22 +5245,13 @@
         <v>Charit</v>
       </c>
       <c r="I116" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
       </c>
       <c r="K116" t="str">
         <v/>
-      </c>
-      <c r="L116" t="str">
-        <v/>
-      </c>
-      <c r="M116" t="str">
-        <v/>
-      </c>
-      <c r="N116">
-        <v>100</v>
       </c>
     </row>
     <row r="117">
@@ -6518,22 +5280,13 @@
         <v>Charit</v>
       </c>
       <c r="I117" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J117">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K117" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L117" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M117" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N117">
-        <v>100</v>
       </c>
     </row>
     <row r="118">
@@ -6562,22 +5315,13 @@
         <v>GITL</v>
       </c>
       <c r="I118" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
       </c>
       <c r="K118" t="str">
         <v/>
-      </c>
-      <c r="L118" t="str">
-        <v/>
-      </c>
-      <c r="M118" t="str">
-        <v/>
-      </c>
-      <c r="N118">
-        <v>100</v>
       </c>
     </row>
     <row r="119">
@@ -6606,22 +5350,13 @@
         <v>GITL</v>
       </c>
       <c r="I119" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
       </c>
       <c r="K119" t="str">
         <v/>
-      </c>
-      <c r="L119" t="str">
-        <v/>
-      </c>
-      <c r="M119" t="str">
-        <v/>
-      </c>
-      <c r="N119">
-        <v>100</v>
       </c>
     </row>
     <row r="120">
@@ -6650,22 +5385,13 @@
         <v>Charit Exp Logis</v>
       </c>
       <c r="I120" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J120">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J120" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K120" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L120" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M120" t="str">
         <v>Charit Exp Logis</v>
-      </c>
-      <c r="N120">
-        <v>100</v>
       </c>
     </row>
     <row r="121">
@@ -6694,22 +5420,13 @@
         <v>GITL User</v>
       </c>
       <c r="I121" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J121">
-        <v>4</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J121" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K121" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L121" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M121" t="str">
         <v>GITL User</v>
-      </c>
-      <c r="N121">
-        <v>100</v>
       </c>
     </row>
     <row r="122">
@@ -6738,22 +5455,13 @@
         <v>GITL</v>
       </c>
       <c r="I122" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
       </c>
       <c r="K122" t="str">
         <v/>
-      </c>
-      <c r="L122" t="str">
-        <v/>
-      </c>
-      <c r="M122" t="str">
-        <v/>
-      </c>
-      <c r="N122">
-        <v>10</v>
       </c>
     </row>
     <row r="123">
@@ -6782,22 +5490,13 @@
         <v>GITL</v>
       </c>
       <c r="I123" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
       </c>
       <c r="K123" t="str">
         <v/>
-      </c>
-      <c r="L123" t="str">
-        <v/>
-      </c>
-      <c r="M123" t="str">
-        <v/>
-      </c>
-      <c r="N123">
-        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6826,22 +5525,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I124" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J124">
-        <v>9</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J124" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K124" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L124" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M124" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N124">
-        <v>95</v>
       </c>
     </row>
     <row r="125">
@@ -6870,22 +5560,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I125" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J125">
-        <v>3</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J125" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K125" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L125" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M125" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N125">
-        <v>95</v>
       </c>
     </row>
     <row r="126">
@@ -6914,22 +5595,13 @@
         <v>Export logistics</v>
       </c>
       <c r="I126" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
       </c>
       <c r="K126" t="str">
         <v/>
-      </c>
-      <c r="L126" t="str">
-        <v/>
-      </c>
-      <c r="M126" t="str">
-        <v/>
-      </c>
-      <c r="N126">
-        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -6958,22 +5630,13 @@
         <v>Charit</v>
       </c>
       <c r="I127" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
       </c>
       <c r="K127" t="str">
         <v/>
-      </c>
-      <c r="L127" t="str">
-        <v/>
-      </c>
-      <c r="M127" t="str">
-        <v/>
-      </c>
-      <c r="N127">
-        <v>100</v>
       </c>
     </row>
     <row r="128">
@@ -7002,22 +5665,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I128" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
       </c>
       <c r="K128" t="str">
         <v/>
-      </c>
-      <c r="L128" t="str">
-        <v/>
-      </c>
-      <c r="M128" t="str">
-        <v/>
-      </c>
-      <c r="N128">
-        <v>100</v>
       </c>
     </row>
     <row r="129">
@@ -7046,22 +5700,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I129" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
       </c>
       <c r="K129" t="str">
         <v/>
-      </c>
-      <c r="L129" t="str">
-        <v/>
-      </c>
-      <c r="M129" t="str">
-        <v/>
-      </c>
-      <c r="N129">
-        <v>100</v>
       </c>
     </row>
     <row r="130">
@@ -7090,22 +5735,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I130" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
       </c>
       <c r="K130" t="str">
         <v/>
-      </c>
-      <c r="L130" t="str">
-        <v/>
-      </c>
-      <c r="M130" t="str">
-        <v/>
-      </c>
-      <c r="N130">
-        <v>100</v>
       </c>
     </row>
     <row r="131">
@@ -7134,22 +5770,13 @@
         <v>Charit</v>
       </c>
       <c r="I131" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
       </c>
       <c r="K131" t="str">
         <v/>
-      </c>
-      <c r="L131" t="str">
-        <v/>
-      </c>
-      <c r="M131" t="str">
-        <v/>
-      </c>
-      <c r="N131">
-        <v>100</v>
       </c>
     </row>
     <row r="132">
@@ -7178,22 +5805,13 @@
         <v>Charit</v>
       </c>
       <c r="I132" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
       </c>
       <c r="K132" t="str">
         <v/>
-      </c>
-      <c r="L132" t="str">
-        <v/>
-      </c>
-      <c r="M132" t="str">
-        <v/>
-      </c>
-      <c r="N132">
-        <v>100</v>
       </c>
     </row>
     <row r="133">
@@ -7222,22 +5840,13 @@
         <v>Charit</v>
       </c>
       <c r="I133" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
       </c>
       <c r="K133" t="str">
         <v/>
-      </c>
-      <c r="L133" t="str">
-        <v/>
-      </c>
-      <c r="M133" t="str">
-        <v/>
-      </c>
-      <c r="N133">
-        <v>100</v>
       </c>
     </row>
     <row r="134">
@@ -7266,22 +5875,13 @@
         <v>Charit</v>
       </c>
       <c r="I134" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
       </c>
       <c r="K134" t="str">
         <v/>
-      </c>
-      <c r="L134" t="str">
-        <v/>
-      </c>
-      <c r="M134" t="str">
-        <v/>
-      </c>
-      <c r="N134">
-        <v>100</v>
       </c>
     </row>
     <row r="135">
@@ -7310,22 +5910,13 @@
         <v>Charit</v>
       </c>
       <c r="I135" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
       </c>
       <c r="K135" t="str">
         <v/>
-      </c>
-      <c r="L135" t="str">
-        <v/>
-      </c>
-      <c r="M135" t="str">
-        <v/>
-      </c>
-      <c r="N135">
-        <v>100</v>
       </c>
     </row>
     <row r="136">
@@ -7354,22 +5945,13 @@
         <v>Charit</v>
       </c>
       <c r="I136" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
       </c>
       <c r="K136" t="str">
         <v/>
-      </c>
-      <c r="L136" t="str">
-        <v/>
-      </c>
-      <c r="M136" t="str">
-        <v/>
-      </c>
-      <c r="N136">
-        <v>100</v>
       </c>
     </row>
     <row r="137">
@@ -7398,22 +5980,13 @@
         <v>GIT Mehrshad</v>
       </c>
       <c r="I137" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
       </c>
       <c r="K137" t="str">
         <v/>
-      </c>
-      <c r="L137" t="str">
-        <v/>
-      </c>
-      <c r="M137" t="str">
-        <v/>
-      </c>
-      <c r="N137">
-        <v>100</v>
       </c>
     </row>
     <row r="138">
@@ -7442,22 +6015,13 @@
         <v>GITL</v>
       </c>
       <c r="I138" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
       </c>
       <c r="K138" t="str">
         <v/>
-      </c>
-      <c r="L138" t="str">
-        <v/>
-      </c>
-      <c r="M138" t="str">
-        <v/>
-      </c>
-      <c r="N138">
-        <v>100</v>
       </c>
     </row>
     <row r="139">
@@ -7486,22 +6050,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I139" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J139">
-        <v>6</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J139" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K139" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L139" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M139" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N139">
-        <v>100</v>
       </c>
     </row>
     <row r="140">
@@ -7530,22 +6085,13 @@
         <v>GITL</v>
       </c>
       <c r="I140" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v/>
       </c>
       <c r="K140" t="str">
         <v/>
-      </c>
-      <c r="L140" t="str">
-        <v/>
-      </c>
-      <c r="M140" t="str">
-        <v/>
-      </c>
-      <c r="N140">
-        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -7574,22 +6120,13 @@
         <v>Charit</v>
       </c>
       <c r="I141" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v/>
       </c>
       <c r="K141" t="str">
         <v/>
-      </c>
-      <c r="L141" t="str">
-        <v/>
-      </c>
-      <c r="M141" t="str">
-        <v/>
-      </c>
-      <c r="N141">
-        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -7618,22 +6155,13 @@
         <v>GITL</v>
       </c>
       <c r="I142" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J142" t="str">
+        <v/>
       </c>
       <c r="K142" t="str">
         <v/>
-      </c>
-      <c r="L142" t="str">
-        <v/>
-      </c>
-      <c r="M142" t="str">
-        <v/>
-      </c>
-      <c r="N142">
-        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -7662,22 +6190,13 @@
         <v>Rama Sir</v>
       </c>
       <c r="I143" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v/>
       </c>
       <c r="K143" t="str">
         <v/>
-      </c>
-      <c r="L143" t="str">
-        <v/>
-      </c>
-      <c r="M143" t="str">
-        <v/>
-      </c>
-      <c r="N143">
-        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -7706,22 +6225,13 @@
         <v>Rama Sir</v>
       </c>
       <c r="I144" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v/>
       </c>
       <c r="K144" t="str">
         <v/>
-      </c>
-      <c r="L144" t="str">
-        <v/>
-      </c>
-      <c r="M144" t="str">
-        <v/>
-      </c>
-      <c r="N144">
-        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -7750,22 +6260,13 @@
         <v>Rama Sir</v>
       </c>
       <c r="I145" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J145">
-        <v>19</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J145" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K145" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L145" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M145" t="str">
         <v>Rama Sir</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -7794,22 +6295,13 @@
         <v>Charit</v>
       </c>
       <c r="I146" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J146">
-        <v>15</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J146" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K146" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L146" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M146" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -7838,22 +6330,13 @@
         <v>Charit</v>
       </c>
       <c r="I147" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v/>
       </c>
       <c r="K147" t="str">
         <v/>
-      </c>
-      <c r="L147" t="str">
-        <v/>
-      </c>
-      <c r="M147" t="str">
-        <v/>
-      </c>
-      <c r="N147">
-        <v>98</v>
       </c>
     </row>
     <row r="148">
@@ -7882,22 +6365,13 @@
         <v>Charit</v>
       </c>
       <c r="I148" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v/>
       </c>
       <c r="K148" t="str">
         <v/>
-      </c>
-      <c r="L148" t="str">
-        <v/>
-      </c>
-      <c r="M148" t="str">
-        <v/>
-      </c>
-      <c r="N148">
-        <v>100</v>
       </c>
     </row>
     <row r="149">
@@ -7926,22 +6400,13 @@
         <v>Charit</v>
       </c>
       <c r="I149" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J149">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J149" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K149" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L149" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M149" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N149">
-        <v>100</v>
       </c>
     </row>
     <row r="150">
@@ -7970,22 +6435,13 @@
         <v>Charit</v>
       </c>
       <c r="I150" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J150">
-        <v>18</v>
+        <v>Pending for CCB. Emailed to Manoj sir with reasons</v>
+      </c>
+      <c r="J150" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K150" t="str">
-        <v>Pending for CCB. Emailed to Manoj sir with reasons</v>
-      </c>
-      <c r="L150" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M150" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N150">
-        <v>95</v>
       </c>
     </row>
     <row r="151">
@@ -8014,22 +6470,13 @@
         <v>Charit</v>
       </c>
       <c r="I151" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v/>
       </c>
       <c r="K151" t="str">
         <v/>
-      </c>
-      <c r="L151" t="str">
-        <v/>
-      </c>
-      <c r="M151" t="str">
-        <v/>
-      </c>
-      <c r="N151">
-        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8058,22 +6505,13 @@
         <v>Charit</v>
       </c>
       <c r="I152" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J152">
-        <v>15</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J152" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K152" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L152" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M152" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -8102,22 +6540,13 @@
         <v>Charit</v>
       </c>
       <c r="I153" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J153">
-        <v>11</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J153" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K153" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L153" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M153" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -8146,22 +6575,13 @@
         <v>Charit</v>
       </c>
       <c r="I154" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J154">
-        <v>8</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J154" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K154" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L154" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M154" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N154">
-        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -8190,22 +6610,13 @@
         <v>Charit</v>
       </c>
       <c r="I155" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J155">
-        <v>1</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J155" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K155" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L155" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M155" t="str">
         <v>Charit</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8234,22 +6645,13 @@
         <v>GITL</v>
       </c>
       <c r="I156" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J156" t="str">
+        <v/>
       </c>
       <c r="K156" t="str">
         <v/>
-      </c>
-      <c r="L156" t="str">
-        <v/>
-      </c>
-      <c r="M156" t="str">
-        <v/>
-      </c>
-      <c r="N156">
-        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -8278,22 +6680,13 @@
         <v>GITL</v>
       </c>
       <c r="I157" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J157">
-        <v>31</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J157" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K157" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L157" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M157" t="str">
         <v>GITL</v>
-      </c>
-      <c r="N157">
-        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -8322,22 +6715,13 @@
         <v>Us &amp; GITL</v>
       </c>
       <c r="I158" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J158">
-        <v>29</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J158" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K158" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L158" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M158" t="str">
         <v>Us &amp; GITL</v>
-      </c>
-      <c r="N158">
-        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -8366,22 +6750,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I159" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J159">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J159" t="str">
+        <v/>
       </c>
       <c r="K159" t="str">
         <v/>
-      </c>
-      <c r="L159" t="str">
-        <v/>
-      </c>
-      <c r="M159" t="str">
-        <v/>
-      </c>
-      <c r="N159">
-        <v>100</v>
       </c>
     </row>
     <row r="160">
@@ -8410,22 +6785,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I160" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J160">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J160" t="str">
+        <v/>
       </c>
       <c r="K160" t="str">
         <v/>
-      </c>
-      <c r="L160" t="str">
-        <v/>
-      </c>
-      <c r="M160" t="str">
-        <v/>
-      </c>
-      <c r="N160">
-        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -8454,22 +6820,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I161" t="str">
-        <v>delayed</v>
-      </c>
-      <c r="J161">
-        <v>14</v>
+        <v>Operational bottlenecks and resource allocation delays.</v>
+      </c>
+      <c r="J161" t="str">
+        <v>Pushed back downstream task completions.</v>
       </c>
       <c r="K161" t="str">
-        <v>Operational bottlenecks and resource allocation delays.</v>
-      </c>
-      <c r="L161" t="str">
-        <v>Pushed back downstream task completions.</v>
-      </c>
-      <c r="M161" t="str">
         <v>Mehrshad</v>
-      </c>
-      <c r="N161">
-        <v>95</v>
       </c>
     </row>
     <row r="162">
@@ -8498,22 +6855,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I162" t="str">
-        <v>in-progress</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J162" t="str">
+        <v/>
       </c>
       <c r="K162" t="str">
         <v/>
-      </c>
-      <c r="L162" t="str">
-        <v/>
-      </c>
-      <c r="M162" t="str">
-        <v/>
-      </c>
-      <c r="N162">
-        <v>33</v>
       </c>
     </row>
     <row r="163">
@@ -8542,22 +6890,13 @@
         <v>Mehrshad</v>
       </c>
       <c r="I163" t="str">
-        <v>not-started</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J163" t="str">
+        <v/>
       </c>
       <c r="K163" t="str">
         <v/>
-      </c>
-      <c r="L163" t="str">
-        <v/>
-      </c>
-      <c r="M163" t="str">
-        <v/>
-      </c>
-      <c r="N163">
-        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -8586,27 +6925,18 @@
         <v>Mehrshad</v>
       </c>
       <c r="I164" t="str">
-        <v>completed</v>
-      </c>
-      <c r="J164">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="J164" t="str">
+        <v/>
       </c>
       <c r="K164" t="str">
         <v/>
-      </c>
-      <c r="L164" t="str">
-        <v/>
-      </c>
-      <c r="M164" t="str">
-        <v/>
-      </c>
-      <c r="N164">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K164"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8966,8 +7296,434 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Project id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>SRF No</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Developments</v>
+      </c>
+      <c r="D1" t="str">
+        <v>User</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Mandays FC</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Mandays TC</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Total Mandays</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Development Cost (INR)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Uploaded On</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Approved On</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Received for CCB</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Send for CCB</v>
+      </c>
+      <c r="N1" t="str">
+        <v>CCB Received On</v>
+      </c>
+      <c r="O1" t="str">
+        <v>CCB Attached in CRS On</v>
+      </c>
+      <c r="P1" t="str">
+        <v>FSD Received On</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>FSD Approved On</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Received for UAT</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Actual Testing &amp; Approval</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SRF Close</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SRF-001-BP-MAPPING</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Form layouts and master data mapping workflows for BP forms integration.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>62500</v>
+      </c>
+      <c r="I2" t="str">
+        <v>CCB Received On</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-02-15</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-02-20</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-02-25</v>
+      </c>
+      <c r="O2" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SRF-002-LA-PO-GEN</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Leasing Automation backend purchase order creation service.</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Mehrshad Nava</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>25</v>
+      </c>
+      <c r="G3">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>100000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>FSD Approved On</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-03-01</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="O3" t="str">
+        <v>2026-03-15</v>
+      </c>
+      <c r="P3" t="str">
+        <v>2026-03-20</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>2026-03-25</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SRF-003-EBRC-FETCH</v>
+      </c>
+      <c r="C4" t="str">
+        <v>electronic Bank Realization Certificate parsing engine &amp; callback listener.</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Ivan</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>125000</v>
+      </c>
+      <c r="I4" t="str">
+        <v>SRF Close</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="K4" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-01-18</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="O4" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="P4" t="str">
+        <v>2026-01-28</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>2026-02-02</v>
+      </c>
+      <c r="R4" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="S4" t="str">
+        <v>2026-02-18</v>
+      </c>
+      <c r="T4" t="str">
+        <v>2026-02-25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SRF-004-FX-MTM-RPT</v>
+      </c>
+      <c r="C5" t="str">
+        <v>MTM Reports data replication and FX What-if analyzer scripts.</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Ananth</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
+        <v>50000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Uploaded On</v>
+      </c>
+      <c r="J5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:T5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Project id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Kaizen Id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Uploaded On</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Approved by L+1</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Approved by L+2</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Grade</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>K1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Automate form field extraction using AI</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-06-10</v>
+      </c>
+      <c r="G2" t="str">
+        <v>L1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>K1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Optimize database index search speed</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>L2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>K1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Streamline Forex hedge decision matrix</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>L3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+  </ignoredErrors>
+</worksheet>
 </file>